--- a/AtchisonRegime/Outputs/USA/df_regSummary_USA.xlsx
+++ b/AtchisonRegime/Outputs/USA/df_regSummary_USA.xlsx
@@ -530,13 +530,13 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="G2" t="n">
-        <v>1.516481591247468</v>
+        <v>1.50507247553915</v>
       </c>
       <c r="H2" t="n">
-        <v>2.697014155346433</v>
+        <v>2.696372498102659</v>
       </c>
       <c r="I2" t="n">
         <v>-5.920958484544303</v>
@@ -545,16 +545,16 @@
         <v>12.09637420237011</v>
       </c>
       <c r="K2" t="n">
-        <v>32.0863309352518</v>
+        <v>32.18390804597701</v>
       </c>
       <c r="L2" t="n">
         <v>23</v>
       </c>
       <c r="M2" t="n">
-        <v>9.695652173913043</v>
+        <v>9.739130434782609</v>
       </c>
       <c r="N2" t="n">
-        <v>0.1612964576781782</v>
+        <v>0.160704355942519</v>
       </c>
       <c r="O2" t="n">
         <v>-0.09487463008282304</v>
@@ -603,7 +603,7 @@
         <v>9.217830822195761</v>
       </c>
       <c r="K3" t="n">
-        <v>19.56834532374101</v>
+        <v>19.54022988505747</v>
       </c>
       <c r="L3" t="n">
         <v>21</v>
@@ -661,7 +661,7 @@
         <v>12.32175011776928</v>
       </c>
       <c r="K4" t="n">
-        <v>21.15107913669065</v>
+        <v>21.12068965517241</v>
       </c>
       <c r="L4" t="n">
         <v>21</v>
@@ -719,7 +719,7 @@
         <v>11.60677491371982</v>
       </c>
       <c r="K5" t="n">
-        <v>27.19424460431655</v>
+        <v>27.1551724137931</v>
       </c>
       <c r="L5" t="n">
         <v>19</v>
@@ -762,13 +762,13 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="G6" t="n">
-        <v>1.817335207728831</v>
+        <v>1.693190385616319</v>
       </c>
       <c r="H6" t="n">
-        <v>4.128712880280975</v>
+        <v>4.21215885625534</v>
       </c>
       <c r="I6" t="n">
         <v>-8.49080820295638</v>
@@ -777,22 +777,22 @@
         <v>8.955800344253511</v>
       </c>
       <c r="K6" t="n">
-        <v>38.75</v>
+        <v>39.1304347826087</v>
       </c>
       <c r="L6" t="n">
         <v>5</v>
       </c>
       <c r="M6" t="n">
-        <v>12.4</v>
+        <v>12.6</v>
       </c>
       <c r="N6" t="n">
-        <v>0.2569565713497336</v>
+        <v>0.2377582999627654</v>
       </c>
       <c r="O6" t="n">
         <v>-0.0260038557337664</v>
       </c>
       <c r="P6" t="n">
-        <v>0.5988463879111421</v>
+        <v>0.5028550309763014</v>
       </c>
     </row>
     <row r="7">
@@ -835,7 +835,7 @@
         <v>10.3135151779801</v>
       </c>
       <c r="K7" t="n">
-        <v>20</v>
+        <v>19.87577639751553</v>
       </c>
       <c r="L7" t="n">
         <v>5</v>
@@ -893,7 +893,7 @@
         <v>9.418745103146341</v>
       </c>
       <c r="K8" t="n">
-        <v>20</v>
+        <v>19.87577639751553</v>
       </c>
       <c r="L8" t="n">
         <v>4</v>
@@ -951,7 +951,7 @@
         <v>11.1380905480897</v>
       </c>
       <c r="K9" t="n">
-        <v>21.25</v>
+        <v>21.11801242236025</v>
       </c>
       <c r="L9" t="n">
         <v>4</v>
@@ -994,13 +994,13 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="G10" t="n">
-        <v>1.729678037418979</v>
+        <v>1.557650277672755</v>
       </c>
       <c r="H10" t="n">
-        <v>4.532677330944555</v>
+        <v>4.69874279299983</v>
       </c>
       <c r="I10" t="n">
         <v>-9.130168483852231</v>
@@ -1009,16 +1009,16 @@
         <v>13.9265910796816</v>
       </c>
       <c r="K10" t="n">
-        <v>38.75</v>
+        <v>39.1304347826087</v>
       </c>
       <c r="L10" t="n">
         <v>5</v>
       </c>
       <c r="M10" t="n">
-        <v>12.4</v>
+        <v>12.6</v>
       </c>
       <c r="N10" t="n">
-        <v>0.250263525543147</v>
+        <v>0.2269994655484361</v>
       </c>
       <c r="O10" t="n">
         <v>-0.038663922363393</v>
@@ -1067,7 +1067,7 @@
         <v>9.04103299082419</v>
       </c>
       <c r="K11" t="n">
-        <v>20</v>
+        <v>19.87577639751553</v>
       </c>
       <c r="L11" t="n">
         <v>5</v>
@@ -1125,7 +1125,7 @@
         <v>9.668123981273439</v>
       </c>
       <c r="K12" t="n">
-        <v>20</v>
+        <v>19.87577639751553</v>
       </c>
       <c r="L12" t="n">
         <v>4</v>
@@ -1183,7 +1183,7 @@
         <v>17.1993335323565</v>
       </c>
       <c r="K13" t="n">
-        <v>21.25</v>
+        <v>21.11801242236025</v>
       </c>
       <c r="L13" t="n">
         <v>4</v>
@@ -1226,13 +1226,13 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="G14" t="n">
-        <v>1.255199854093324</v>
+        <v>1.330316098170085</v>
       </c>
       <c r="H14" t="n">
-        <v>3.297952272619971</v>
+        <v>3.325137035561665</v>
       </c>
       <c r="I14" t="n">
         <v>-4.66984504576325</v>
@@ -1241,16 +1241,16 @@
         <v>9.823783930802669</v>
       </c>
       <c r="K14" t="n">
-        <v>38.75</v>
+        <v>39.1304347826087</v>
       </c>
       <c r="L14" t="n">
         <v>5</v>
       </c>
       <c r="M14" t="n">
-        <v>12.4</v>
+        <v>12.6</v>
       </c>
       <c r="N14" t="n">
-        <v>0.1784807312402021</v>
+        <v>0.1936187364696616</v>
       </c>
       <c r="O14" t="n">
         <v>-0.03344483363254391</v>
@@ -1299,7 +1299,7 @@
         <v>7.74527627402691</v>
       </c>
       <c r="K15" t="n">
-        <v>20</v>
+        <v>19.87577639751553</v>
       </c>
       <c r="L15" t="n">
         <v>5</v>
@@ -1357,7 +1357,7 @@
         <v>10.3641980528429</v>
       </c>
       <c r="K16" t="n">
-        <v>20</v>
+        <v>19.87577639751553</v>
       </c>
       <c r="L16" t="n">
         <v>4</v>
@@ -1415,7 +1415,7 @@
         <v>9.57292159347422</v>
       </c>
       <c r="K17" t="n">
-        <v>21.25</v>
+        <v>21.11801242236025</v>
       </c>
       <c r="L17" t="n">
         <v>4</v>
@@ -1458,13 +1458,13 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="G18" t="n">
-        <v>1.274342131833923</v>
+        <v>1.31890453902616</v>
       </c>
       <c r="H18" t="n">
-        <v>6.003194643687698</v>
+        <v>5.965080736960624</v>
       </c>
       <c r="I18" t="n">
         <v>-11.8320411519501</v>
@@ -1473,16 +1473,16 @@
         <v>21.6010537672175</v>
       </c>
       <c r="K18" t="n">
-        <v>38.75</v>
+        <v>39.1304347826087</v>
       </c>
       <c r="L18" t="n">
         <v>5</v>
       </c>
       <c r="M18" t="n">
-        <v>12.4</v>
+        <v>12.6</v>
       </c>
       <c r="N18" t="n">
-        <v>0.1662917430822683</v>
+        <v>0.1767191829623444</v>
       </c>
       <c r="O18" t="n">
         <v>-0.1283343741738839</v>
@@ -1531,7 +1531,7 @@
         <v>11.4844653113646</v>
       </c>
       <c r="K19" t="n">
-        <v>20</v>
+        <v>19.87577639751553</v>
       </c>
       <c r="L19" t="n">
         <v>5</v>
@@ -1589,7 +1589,7 @@
         <v>9.63714932872772</v>
       </c>
       <c r="K20" t="n">
-        <v>20</v>
+        <v>19.87577639751553</v>
       </c>
       <c r="L20" t="n">
         <v>4</v>
@@ -1647,7 +1647,7 @@
         <v>25.6080879391498</v>
       </c>
       <c r="K21" t="n">
-        <v>21.25</v>
+        <v>21.11801242236025</v>
       </c>
       <c r="L21" t="n">
         <v>4</v>
@@ -1690,13 +1690,13 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="G22" t="n">
-        <v>2.29098455622489</v>
+        <v>2.281315888815698</v>
       </c>
       <c r="H22" t="n">
-        <v>4.517860264604721</v>
+        <v>4.481934865700838</v>
       </c>
       <c r="I22" t="n">
         <v>-7.834552959385981</v>
@@ -1705,16 +1705,16 @@
         <v>14.7955721617363</v>
       </c>
       <c r="K22" t="n">
-        <v>38.75</v>
+        <v>39.1304347826087</v>
       </c>
       <c r="L22" t="n">
         <v>5</v>
       </c>
       <c r="M22" t="n">
-        <v>12.4</v>
+        <v>12.6</v>
       </c>
       <c r="N22" t="n">
-        <v>0.3497317708204247</v>
+        <v>0.3551572469557611</v>
       </c>
       <c r="O22" t="n">
         <v>-0.04384403286972716</v>
@@ -1763,7 +1763,7 @@
         <v>17.2630481734445</v>
       </c>
       <c r="K23" t="n">
-        <v>20</v>
+        <v>19.87577639751553</v>
       </c>
       <c r="L23" t="n">
         <v>5</v>
@@ -1821,7 +1821,7 @@
         <v>9.959724493416481</v>
       </c>
       <c r="K24" t="n">
-        <v>20</v>
+        <v>19.87577639751553</v>
       </c>
       <c r="L24" t="n">
         <v>4</v>
@@ -1879,7 +1879,7 @@
         <v>12.5443599847335</v>
       </c>
       <c r="K25" t="n">
-        <v>21.25</v>
+        <v>21.11801242236025</v>
       </c>
       <c r="L25" t="n">
         <v>4</v>
@@ -1922,13 +1922,13 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="G26" t="n">
-        <v>1.591603206236816</v>
+        <v>1.59435067319945</v>
       </c>
       <c r="H26" t="n">
-        <v>3.401809869290509</v>
+        <v>3.374334864751869</v>
       </c>
       <c r="I26" t="n">
         <v>-4.70593736639751</v>
@@ -1937,16 +1937,16 @@
         <v>9.96890693734484</v>
       </c>
       <c r="K26" t="n">
-        <v>38.75</v>
+        <v>39.1304347826087</v>
       </c>
       <c r="L26" t="n">
         <v>5</v>
       </c>
       <c r="M26" t="n">
-        <v>12.4</v>
+        <v>12.6</v>
       </c>
       <c r="N26" t="n">
-        <v>0.2492382914820463</v>
+        <v>0.2534689711025697</v>
       </c>
       <c r="O26" t="n">
         <v>-0.03629388667361888</v>
@@ -1995,7 +1995,7 @@
         <v>8.86970753112975</v>
       </c>
       <c r="K27" t="n">
-        <v>20</v>
+        <v>19.87577639751553</v>
       </c>
       <c r="L27" t="n">
         <v>5</v>
@@ -2053,7 +2053,7 @@
         <v>7.651278631372289</v>
       </c>
       <c r="K28" t="n">
-        <v>20</v>
+        <v>19.87577639751553</v>
       </c>
       <c r="L28" t="n">
         <v>4</v>
@@ -2111,7 +2111,7 @@
         <v>10.2757108623477</v>
       </c>
       <c r="K29" t="n">
-        <v>21.25</v>
+        <v>21.11801242236025</v>
       </c>
       <c r="L29" t="n">
         <v>4</v>
@@ -2154,13 +2154,13 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="G30" t="n">
-        <v>1.939399161532498</v>
+        <v>1.88979785231731</v>
       </c>
       <c r="H30" t="n">
-        <v>4.183119601461454</v>
+        <v>4.16788365469603</v>
       </c>
       <c r="I30" t="n">
         <v>-5.93862228897025</v>
@@ -2169,16 +2169,16 @@
         <v>13.5073547998131</v>
       </c>
       <c r="K30" t="n">
-        <v>38.75</v>
+        <v>39.1304347826087</v>
       </c>
       <c r="L30" t="n">
         <v>5</v>
       </c>
       <c r="M30" t="n">
-        <v>12.4</v>
+        <v>12.6</v>
       </c>
       <c r="N30" t="n">
-        <v>0.2855275258317235</v>
+        <v>0.2823707548130373</v>
       </c>
       <c r="O30" t="n">
         <v>-0.006648237576164506</v>
@@ -2227,7 +2227,7 @@
         <v>11.9900891508605</v>
       </c>
       <c r="K31" t="n">
-        <v>20</v>
+        <v>19.87577639751553</v>
       </c>
       <c r="L31" t="n">
         <v>5</v>
@@ -2285,7 +2285,7 @@
         <v>7.456744942287171</v>
       </c>
       <c r="K32" t="n">
-        <v>20</v>
+        <v>19.87577639751553</v>
       </c>
       <c r="L32" t="n">
         <v>4</v>
@@ -2343,7 +2343,7 @@
         <v>14.5269451461826</v>
       </c>
       <c r="K33" t="n">
-        <v>21.25</v>
+        <v>21.11801242236025</v>
       </c>
       <c r="L33" t="n">
         <v>4</v>
@@ -2386,13 +2386,13 @@
         </is>
       </c>
       <c r="F34" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="G34" t="n">
-        <v>2.093851115554846</v>
+        <v>2.043950641208566</v>
       </c>
       <c r="H34" t="n">
-        <v>4.267889535836972</v>
+        <v>4.251819175111586</v>
       </c>
       <c r="I34" t="n">
         <v>-9.03342228644261</v>
@@ -2401,16 +2401,16 @@
         <v>13.0963168927553</v>
       </c>
       <c r="K34" t="n">
-        <v>38.75</v>
+        <v>39.1304347826087</v>
       </c>
       <c r="L34" t="n">
         <v>5</v>
       </c>
       <c r="M34" t="n">
-        <v>12.4</v>
+        <v>12.6</v>
       </c>
       <c r="N34" t="n">
-        <v>0.3013602524333251</v>
+        <v>0.2984125510387441</v>
       </c>
       <c r="O34" t="n">
         <v>0.0376879500447278</v>
@@ -2459,7 +2459,7 @@
         <v>10.24694135888</v>
       </c>
       <c r="K35" t="n">
-        <v>20</v>
+        <v>19.87577639751553</v>
       </c>
       <c r="L35" t="n">
         <v>5</v>
@@ -2517,7 +2517,7 @@
         <v>11.138619523777</v>
       </c>
       <c r="K36" t="n">
-        <v>20</v>
+        <v>19.87577639751553</v>
       </c>
       <c r="L36" t="n">
         <v>4</v>
@@ -2575,7 +2575,7 @@
         <v>11.8700581470654</v>
       </c>
       <c r="K37" t="n">
-        <v>21.25</v>
+        <v>21.11801242236025</v>
       </c>
       <c r="L37" t="n">
         <v>4</v>
@@ -2618,13 +2618,13 @@
         </is>
       </c>
       <c r="F38" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="G38" t="n">
-        <v>1.473376362221011</v>
+        <v>1.453965102335928</v>
       </c>
       <c r="H38" t="n">
-        <v>3.612573251183403</v>
+        <v>3.586631954839385</v>
       </c>
       <c r="I38" t="n">
         <v>-6.119052067979229</v>
@@ -2633,16 +2633,16 @@
         <v>10.2371026217823</v>
       </c>
       <c r="K38" t="n">
-        <v>38.75</v>
+        <v>39.1304347826087</v>
       </c>
       <c r="L38" t="n">
         <v>5</v>
       </c>
       <c r="M38" t="n">
-        <v>12.4</v>
+        <v>12.6</v>
       </c>
       <c r="N38" t="n">
-        <v>0.2161631940696445</v>
+        <v>0.2167319629055521</v>
       </c>
       <c r="O38" t="n">
         <v>-0.02919700639085454</v>
@@ -2691,7 +2691,7 @@
         <v>9.97010822270626</v>
       </c>
       <c r="K39" t="n">
-        <v>20</v>
+        <v>19.87577639751553</v>
       </c>
       <c r="L39" t="n">
         <v>5</v>
@@ -2749,7 +2749,7 @@
         <v>11.7139405168735</v>
       </c>
       <c r="K40" t="n">
-        <v>20</v>
+        <v>19.87577639751553</v>
       </c>
       <c r="L40" t="n">
         <v>4</v>
@@ -2807,7 +2807,7 @@
         <v>9.589243507641781</v>
       </c>
       <c r="K41" t="n">
-        <v>21.25</v>
+        <v>21.11801242236025</v>
       </c>
       <c r="L41" t="n">
         <v>4</v>
@@ -2850,13 +2850,13 @@
         </is>
       </c>
       <c r="F42" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G42" t="n">
-        <v>1.033442711355242</v>
+        <v>1.129899417120397</v>
       </c>
       <c r="H42" t="n">
-        <v>4.070343018551587</v>
+        <v>4.053303579919326</v>
       </c>
       <c r="I42" t="n">
         <v>-8.10424767618815</v>
@@ -2865,22 +2865,22 @@
         <v>9.6248306252491</v>
       </c>
       <c r="K42" t="n">
-        <v>34.31372549019608</v>
+        <v>34.95145631067961</v>
       </c>
       <c r="L42" t="n">
         <v>3</v>
       </c>
       <c r="M42" t="n">
-        <v>11.66666666666667</v>
+        <v>12</v>
       </c>
       <c r="N42" t="n">
-        <v>0.1210484640780234</v>
+        <v>0.1396401339150191</v>
       </c>
       <c r="O42" t="n">
         <v>0.007551522381175291</v>
       </c>
       <c r="P42" t="n">
-        <v>0.2378260967038175</v>
+        <v>0.2936011062148047</v>
       </c>
     </row>
     <row r="43">
@@ -2923,7 +2923,7 @@
         <v>6.84469377692436</v>
       </c>
       <c r="K43" t="n">
-        <v>25.49019607843137</v>
+        <v>25.24271844660194</v>
       </c>
       <c r="L43" t="n">
         <v>4</v>
@@ -2981,7 +2981,7 @@
         <v>7.202297448723289</v>
       </c>
       <c r="K44" t="n">
-        <v>8.823529411764707</v>
+        <v>8.737864077669903</v>
       </c>
       <c r="L44" t="n">
         <v>2</v>
@@ -3039,7 +3039,7 @@
         <v>7.360199774148531</v>
       </c>
       <c r="K45" t="n">
-        <v>31.37254901960784</v>
+        <v>31.06796116504854</v>
       </c>
       <c r="L45" t="n">
         <v>3</v>
@@ -3082,13 +3082,13 @@
         </is>
       </c>
       <c r="F46" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="G46" t="n">
-        <v>1.253244686663834</v>
+        <v>1.262625270001743</v>
       </c>
       <c r="H46" t="n">
-        <v>4.441448997007622</v>
+        <v>4.406114392718932</v>
       </c>
       <c r="I46" t="n">
         <v>-7.088565609126809</v>
@@ -3097,16 +3097,16 @@
         <v>12.2158962489732</v>
       </c>
       <c r="K46" t="n">
-        <v>38.75</v>
+        <v>39.1304347826087</v>
       </c>
       <c r="L46" t="n">
         <v>5</v>
       </c>
       <c r="M46" t="n">
-        <v>12.4</v>
+        <v>12.6</v>
       </c>
       <c r="N46" t="n">
-        <v>0.1674438087671844</v>
+        <v>0.1723852192576477</v>
       </c>
       <c r="O46" t="n">
         <v>-0.0430587583608022</v>
@@ -3155,7 +3155,7 @@
         <v>7.714682238485699</v>
       </c>
       <c r="K47" t="n">
-        <v>20</v>
+        <v>19.87577639751553</v>
       </c>
       <c r="L47" t="n">
         <v>5</v>
@@ -3213,7 +3213,7 @@
         <v>10.9879016302789</v>
       </c>
       <c r="K48" t="n">
-        <v>20</v>
+        <v>19.87577639751553</v>
       </c>
       <c r="L48" t="n">
         <v>4</v>
@@ -3271,7 +3271,7 @@
         <v>6.83944264356443</v>
       </c>
       <c r="K49" t="n">
-        <v>21.25</v>
+        <v>21.11801242236025</v>
       </c>
       <c r="L49" t="n">
         <v>4</v>
@@ -3314,37 +3314,37 @@
         </is>
       </c>
       <c r="F50" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="G50" t="n">
-        <v>1.542439071048227</v>
+        <v>1.308689114876782</v>
       </c>
       <c r="H50" t="n">
-        <v>3.24235854617211</v>
+        <v>3.55134634593727</v>
       </c>
       <c r="I50" t="n">
-        <v>-5.54358074682365</v>
+        <v>-8.508809044323931</v>
       </c>
       <c r="J50" t="n">
         <v>6.95169290448147</v>
       </c>
       <c r="K50" t="n">
-        <v>32.55813953488372</v>
+        <v>33.07692307692307</v>
       </c>
       <c r="L50" t="n">
         <v>5</v>
       </c>
       <c r="M50" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="N50" t="n">
-        <v>0.1423933908336546</v>
+        <v>0.1184859468952383</v>
       </c>
       <c r="O50" t="n">
         <v>-0.02750881203672606</v>
       </c>
       <c r="P50" t="n">
-        <v>0.4048642891078003</v>
+        <v>0.2853270694157186</v>
       </c>
     </row>
     <row r="51">
@@ -3387,7 +3387,7 @@
         <v>7.285268265153571</v>
       </c>
       <c r="K51" t="n">
-        <v>20.15503875968992</v>
+        <v>20</v>
       </c>
       <c r="L51" t="n">
         <v>4</v>
@@ -3445,7 +3445,7 @@
         <v>7.521483003263831</v>
       </c>
       <c r="K52" t="n">
-        <v>22.48062015503876</v>
+        <v>22.30769230769231</v>
       </c>
       <c r="L52" t="n">
         <v>3</v>
@@ -3503,7 +3503,7 @@
         <v>8.975974874825891</v>
       </c>
       <c r="K53" t="n">
-        <v>24.8062015503876</v>
+        <v>24.61538461538462</v>
       </c>
       <c r="L53" t="n">
         <v>3</v>
@@ -3546,37 +3546,37 @@
         </is>
       </c>
       <c r="F54" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="G54" t="n">
-        <v>1.480901384204729</v>
+        <v>1.224987196284963</v>
       </c>
       <c r="H54" t="n">
-        <v>3.279096359932725</v>
+        <v>3.648646427811727</v>
       </c>
       <c r="I54" t="n">
-        <v>-5.82279192050039</v>
+        <v>-9.523408696345211</v>
       </c>
       <c r="J54" t="n">
         <v>7.6716417531022</v>
       </c>
       <c r="K54" t="n">
-        <v>32.55813953488372</v>
+        <v>33.07692307692307</v>
       </c>
       <c r="L54" t="n">
         <v>5</v>
       </c>
       <c r="M54" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="N54" t="n">
-        <v>0.1339981301961045</v>
+        <v>0.1081754616665886</v>
       </c>
       <c r="O54" t="n">
         <v>-0.02026323853882039</v>
       </c>
       <c r="P54" t="n">
-        <v>0.3557471569725745</v>
+        <v>0.2266338143249953</v>
       </c>
     </row>
     <row r="55">
@@ -3619,7 +3619,7 @@
         <v>6.94715275176028</v>
       </c>
       <c r="K55" t="n">
-        <v>20.15503875968992</v>
+        <v>20</v>
       </c>
       <c r="L55" t="n">
         <v>4</v>
@@ -3677,7 +3677,7 @@
         <v>7.13073476203116</v>
       </c>
       <c r="K56" t="n">
-        <v>22.48062015503876</v>
+        <v>22.30769230769231</v>
       </c>
       <c r="L56" t="n">
         <v>3</v>
@@ -3735,7 +3735,7 @@
         <v>7.925364439758551</v>
       </c>
       <c r="K57" t="n">
-        <v>24.8062015503876</v>
+        <v>24.61538461538462</v>
       </c>
       <c r="L57" t="n">
         <v>3</v>
@@ -3778,37 +3778,37 @@
         </is>
       </c>
       <c r="F58" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="G58" t="n">
-        <v>1.351951188266407</v>
+        <v>1.121544945711472</v>
       </c>
       <c r="H58" t="n">
-        <v>3.264579378436513</v>
+        <v>3.561807350733982</v>
       </c>
       <c r="I58" t="n">
-        <v>-4.41020346327878</v>
+        <v>-8.555517241595799</v>
       </c>
       <c r="J58" t="n">
         <v>7.36666934510836</v>
       </c>
       <c r="K58" t="n">
-        <v>32.55813953488372</v>
+        <v>33.07692307692307</v>
       </c>
       <c r="L58" t="n">
         <v>5</v>
       </c>
       <c r="M58" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="N58" t="n">
-        <v>0.1237357192886825</v>
+        <v>0.09954799099203782</v>
       </c>
       <c r="O58" t="n">
         <v>-0.01152848052935629</v>
       </c>
       <c r="P58" t="n">
-        <v>0.4135748671656625</v>
+        <v>0.2926362256824393</v>
       </c>
     </row>
     <row r="59">
@@ -3851,7 +3851,7 @@
         <v>7.93887645673724</v>
       </c>
       <c r="K59" t="n">
-        <v>20.15503875968992</v>
+        <v>20</v>
       </c>
       <c r="L59" t="n">
         <v>4</v>
@@ -3909,7 +3909,7 @@
         <v>8.375876401854281</v>
       </c>
       <c r="K60" t="n">
-        <v>22.48062015503876</v>
+        <v>22.30769230769231</v>
       </c>
       <c r="L60" t="n">
         <v>3</v>
@@ -3967,7 +3967,7 @@
         <v>6.87229435690348</v>
       </c>
       <c r="K61" t="n">
-        <v>24.8062015503876</v>
+        <v>24.61538461538462</v>
       </c>
       <c r="L61" t="n">
         <v>3</v>
@@ -4010,37 +4010,37 @@
         </is>
       </c>
       <c r="F62" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="G62" t="n">
-        <v>1.674763436267108</v>
+        <v>1.376336791123065</v>
       </c>
       <c r="H62" t="n">
-        <v>3.229643246726068</v>
+        <v>3.743228803862341</v>
       </c>
       <c r="I62" t="n">
-        <v>-5.997547424664449</v>
+        <v>-11.1575823049267</v>
       </c>
       <c r="J62" t="n">
         <v>6.89263768827785</v>
       </c>
       <c r="K62" t="n">
-        <v>32.55813953488372</v>
+        <v>33.07692307692307</v>
       </c>
       <c r="L62" t="n">
         <v>5</v>
       </c>
       <c r="M62" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="N62" t="n">
-        <v>0.1548793911144378</v>
+        <v>0.1233762685115819</v>
       </c>
       <c r="O62" t="n">
         <v>-0.01208145336572686</v>
       </c>
       <c r="P62" t="n">
-        <v>0.4117360617158783</v>
+        <v>0.2542204487015984</v>
       </c>
     </row>
     <row r="63">
@@ -4083,7 +4083,7 @@
         <v>7.2021582714579</v>
       </c>
       <c r="K63" t="n">
-        <v>20.15503875968992</v>
+        <v>20</v>
       </c>
       <c r="L63" t="n">
         <v>4</v>
@@ -4141,7 +4141,7 @@
         <v>7.17869308850433</v>
       </c>
       <c r="K64" t="n">
-        <v>22.48062015503876</v>
+        <v>22.30769230769231</v>
       </c>
       <c r="L64" t="n">
         <v>3</v>
@@ -4199,7 +4199,7 @@
         <v>8.24611022911178</v>
       </c>
       <c r="K65" t="n">
-        <v>24.8062015503876</v>
+        <v>24.61538461538462</v>
       </c>
       <c r="L65" t="n">
         <v>3</v>
@@ -4242,37 +4242,37 @@
         </is>
       </c>
       <c r="F66" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="G66" t="n">
-        <v>1.852079742450122</v>
+        <v>1.581408455357284</v>
       </c>
       <c r="H66" t="n">
-        <v>3.93481658177471</v>
+        <v>4.393631911096492</v>
       </c>
       <c r="I66" t="n">
-        <v>-6.747234236335339</v>
+        <v>-13.3055123347488</v>
       </c>
       <c r="J66" t="n">
         <v>11.7483945325047</v>
       </c>
       <c r="K66" t="n">
-        <v>38.73239436619718</v>
+        <v>39.16083916083916</v>
       </c>
       <c r="L66" t="n">
         <v>5</v>
       </c>
       <c r="M66" t="n">
-        <v>11</v>
+        <v>11.2</v>
       </c>
       <c r="N66" t="n">
-        <v>0.2290583342417606</v>
+        <v>0.1888311571191753</v>
       </c>
       <c r="O66" t="n">
         <v>-0.01023538750965192</v>
       </c>
       <c r="P66" t="n">
-        <v>0.5116733617813327</v>
+        <v>0.3928046843520732</v>
       </c>
     </row>
     <row r="67">
@@ -4315,7 +4315,7 @@
         <v>7.42189952260202</v>
       </c>
       <c r="K67" t="n">
-        <v>18.30985915492958</v>
+        <v>18.18181818181818</v>
       </c>
       <c r="L67" t="n">
         <v>4</v>
@@ -4373,7 +4373,7 @@
         <v>8.541253775102129</v>
       </c>
       <c r="K68" t="n">
-        <v>20.42253521126761</v>
+        <v>20.27972027972028</v>
       </c>
       <c r="L68" t="n">
         <v>3</v>
@@ -4431,7 +4431,7 @@
         <v>13.1224591254952</v>
       </c>
       <c r="K69" t="n">
-        <v>22.53521126760564</v>
+        <v>22.37762237762238</v>
       </c>
       <c r="L69" t="n">
         <v>3</v>
@@ -4474,37 +4474,37 @@
         </is>
       </c>
       <c r="F70" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="G70" t="n">
-        <v>1.611249289018029</v>
+        <v>1.374051827623967</v>
       </c>
       <c r="H70" t="n">
-        <v>3.343978758250776</v>
+        <v>3.758934545501023</v>
       </c>
       <c r="I70" t="n">
-        <v>-6.02684421181042</v>
+        <v>-11.6718085490494</v>
       </c>
       <c r="J70" t="n">
         <v>8.538804320682219</v>
       </c>
       <c r="K70" t="n">
-        <v>38.73239436619718</v>
+        <v>39.16083916083916</v>
       </c>
       <c r="L70" t="n">
         <v>5</v>
       </c>
       <c r="M70" t="n">
-        <v>11</v>
+        <v>11.2</v>
       </c>
       <c r="N70" t="n">
-        <v>0.1956956467076387</v>
+        <v>0.1627384891323143</v>
       </c>
       <c r="O70" t="n">
         <v>-0.01060235851672997</v>
       </c>
       <c r="P70" t="n">
-        <v>0.4118273717747234</v>
+        <v>0.337710289520283</v>
       </c>
     </row>
     <row r="71">
@@ -4547,7 +4547,7 @@
         <v>8.076570009882129</v>
       </c>
       <c r="K71" t="n">
-        <v>18.30985915492958</v>
+        <v>18.18181818181818</v>
       </c>
       <c r="L71" t="n">
         <v>4</v>
@@ -4605,7 +4605,7 @@
         <v>7.72617150656165</v>
       </c>
       <c r="K72" t="n">
-        <v>20.42253521126761</v>
+        <v>20.27972027972028</v>
       </c>
       <c r="L72" t="n">
         <v>3</v>
@@ -4663,7 +4663,7 @@
         <v>7.69497967124499</v>
       </c>
       <c r="K73" t="n">
-        <v>22.53521126760564</v>
+        <v>22.37762237762238</v>
       </c>
       <c r="L73" t="n">
         <v>3</v>
@@ -4706,37 +4706,37 @@
         </is>
       </c>
       <c r="F74" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="G74" t="n">
-        <v>1.427856165170456</v>
+        <v>1.180255717123087</v>
       </c>
       <c r="H74" t="n">
-        <v>3.338090341682212</v>
+        <v>3.648201252015532</v>
       </c>
       <c r="I74" t="n">
-        <v>-4.88900426378396</v>
+        <v>-8.47616175672427</v>
       </c>
       <c r="J74" t="n">
         <v>7.79885715856029</v>
       </c>
       <c r="K74" t="n">
-        <v>31.70731707317073</v>
+        <v>32.25806451612903</v>
       </c>
       <c r="L74" t="n">
         <v>4</v>
       </c>
       <c r="M74" t="n">
-        <v>9.75</v>
+        <v>10</v>
       </c>
       <c r="N74" t="n">
-        <v>0.1514102785121009</v>
+        <v>0.123231555519747</v>
       </c>
       <c r="O74" t="n">
         <v>-0.0119688944570685</v>
       </c>
       <c r="P74" t="n">
-        <v>0.3297869389997989</v>
+        <v>0.2556739569809678</v>
       </c>
     </row>
     <row r="75">
@@ -4779,7 +4779,7 @@
         <v>7.56280518804586</v>
       </c>
       <c r="K75" t="n">
-        <v>21.13821138211382</v>
+        <v>20.96774193548387</v>
       </c>
       <c r="L75" t="n">
         <v>4</v>
@@ -4837,7 +4837,7 @@
         <v>6.989405251611849</v>
       </c>
       <c r="K76" t="n">
-        <v>21.13821138211382</v>
+        <v>20.96774193548387</v>
       </c>
       <c r="L76" t="n">
         <v>3</v>
@@ -4895,7 +4895,7 @@
         <v>9.52544316828399</v>
       </c>
       <c r="K77" t="n">
-        <v>26.01626016260163</v>
+        <v>25.80645161290322</v>
       </c>
       <c r="L77" t="n">
         <v>3</v>

--- a/AtchisonRegime/Outputs/USA/df_regSummary_USA.xlsx
+++ b/AtchisonRegime/Outputs/USA/df_regSummary_USA.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P77"/>
+  <dimension ref="A1:P93"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -530,13 +530,13 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="G2" t="n">
-        <v>1.50507247553915</v>
+        <v>1.516481591247468</v>
       </c>
       <c r="H2" t="n">
-        <v>2.696372498102659</v>
+        <v>2.697014155346433</v>
       </c>
       <c r="I2" t="n">
         <v>-5.920958484544303</v>
@@ -545,16 +545,16 @@
         <v>12.09637420237011</v>
       </c>
       <c r="K2" t="n">
-        <v>32.18390804597701</v>
+        <v>31.99426111908178</v>
       </c>
       <c r="L2" t="n">
         <v>23</v>
       </c>
       <c r="M2" t="n">
-        <v>9.739130434782609</v>
+        <v>9.695652173913043</v>
       </c>
       <c r="N2" t="n">
-        <v>0.160704355942519</v>
+        <v>0.1612964576781782</v>
       </c>
       <c r="O2" t="n">
         <v>-0.09487463008282304</v>
@@ -603,7 +603,7 @@
         <v>9.217830822195761</v>
       </c>
       <c r="K3" t="n">
-        <v>19.54022988505747</v>
+        <v>19.51219512195122</v>
       </c>
       <c r="L3" t="n">
         <v>21</v>
@@ -646,13 +646,13 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="G4" t="n">
-        <v>0.7608815328057781</v>
+        <v>0.7664124010957496</v>
       </c>
       <c r="H4" t="n">
-        <v>3.5110956159429</v>
+        <v>3.526078736070417</v>
       </c>
       <c r="I4" t="n">
         <v>-10.75849917490121</v>
@@ -661,16 +661,16 @@
         <v>12.32175011776928</v>
       </c>
       <c r="K4" t="n">
-        <v>21.12068965517241</v>
+        <v>21.37733142037303</v>
       </c>
       <c r="L4" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="M4" t="n">
-        <v>7</v>
+        <v>6.772727272727272</v>
       </c>
       <c r="N4" t="n">
-        <v>0.05626852755431809</v>
+        <v>0.05469268199246653</v>
       </c>
       <c r="O4" t="n">
         <v>-0.1536265717473903</v>
@@ -719,7 +719,7 @@
         <v>11.60677491371982</v>
       </c>
       <c r="K5" t="n">
-        <v>27.1551724137931</v>
+        <v>27.11621233859398</v>
       </c>
       <c r="L5" t="n">
         <v>19</v>
@@ -762,13 +762,13 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="G6" t="n">
-        <v>1.693190385616319</v>
+        <v>1.817335207728831</v>
       </c>
       <c r="H6" t="n">
-        <v>4.21215885625534</v>
+        <v>4.128712880280975</v>
       </c>
       <c r="I6" t="n">
         <v>-8.49080820295638</v>
@@ -777,22 +777,22 @@
         <v>8.955800344253511</v>
       </c>
       <c r="K6" t="n">
-        <v>39.1304347826087</v>
+        <v>38.2716049382716</v>
       </c>
       <c r="L6" t="n">
         <v>5</v>
       </c>
       <c r="M6" t="n">
-        <v>12.6</v>
+        <v>12.4</v>
       </c>
       <c r="N6" t="n">
-        <v>0.2377582999627654</v>
+        <v>0.2569565713497336</v>
       </c>
       <c r="O6" t="n">
         <v>-0.0260038557337664</v>
       </c>
       <c r="P6" t="n">
-        <v>0.5028550309763014</v>
+        <v>0.5988463879111421</v>
       </c>
     </row>
     <row r="7">
@@ -835,7 +835,7 @@
         <v>10.3135151779801</v>
       </c>
       <c r="K7" t="n">
-        <v>19.87577639751553</v>
+        <v>19.75308641975309</v>
       </c>
       <c r="L7" t="n">
         <v>5</v>
@@ -878,13 +878,13 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="G8" t="n">
-        <v>1.236654779132533</v>
+        <v>1.37189595591855</v>
       </c>
       <c r="H8" t="n">
-        <v>3.535992586006569</v>
+        <v>3.721847852811584</v>
       </c>
       <c r="I8" t="n">
         <v>-4.44559447216598</v>
@@ -893,16 +893,16 @@
         <v>9.418745103146341</v>
       </c>
       <c r="K8" t="n">
-        <v>19.87577639751553</v>
+        <v>20.98765432098765</v>
       </c>
       <c r="L8" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M8" t="n">
-        <v>8</v>
+        <v>6.8</v>
       </c>
       <c r="N8" t="n">
-        <v>0.1080811231215166</v>
+        <v>0.1002622429611449</v>
       </c>
       <c r="O8" t="n">
         <v>-0.04096620966264153</v>
@@ -951,7 +951,7 @@
         <v>11.1380905480897</v>
       </c>
       <c r="K9" t="n">
-        <v>21.11801242236025</v>
+        <v>20.98765432098765</v>
       </c>
       <c r="L9" t="n">
         <v>4</v>
@@ -994,13 +994,13 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="G10" t="n">
-        <v>1.557650277672755</v>
+        <v>1.729678037418979</v>
       </c>
       <c r="H10" t="n">
-        <v>4.69874279299983</v>
+        <v>4.532677330944555</v>
       </c>
       <c r="I10" t="n">
         <v>-9.130168483852231</v>
@@ -1009,16 +1009,16 @@
         <v>13.9265910796816</v>
       </c>
       <c r="K10" t="n">
-        <v>39.1304347826087</v>
+        <v>38.2716049382716</v>
       </c>
       <c r="L10" t="n">
         <v>5</v>
       </c>
       <c r="M10" t="n">
-        <v>12.6</v>
+        <v>12.4</v>
       </c>
       <c r="N10" t="n">
-        <v>0.2269994655484361</v>
+        <v>0.250263525543147</v>
       </c>
       <c r="O10" t="n">
         <v>-0.038663922363393</v>
@@ -1067,7 +1067,7 @@
         <v>9.04103299082419</v>
       </c>
       <c r="K11" t="n">
-        <v>19.87577639751553</v>
+        <v>19.75308641975309</v>
       </c>
       <c r="L11" t="n">
         <v>5</v>
@@ -1110,13 +1110,13 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="G12" t="n">
-        <v>1.949990486036811</v>
+        <v>2.007931652282985</v>
       </c>
       <c r="H12" t="n">
-        <v>3.98669221684581</v>
+        <v>4.131130799882667</v>
       </c>
       <c r="I12" t="n">
         <v>-6.1677509153966</v>
@@ -1125,16 +1125,16 @@
         <v>9.668123981273439</v>
       </c>
       <c r="K12" t="n">
-        <v>19.87577639751553</v>
+        <v>20.98765432098765</v>
       </c>
       <c r="L12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M12" t="n">
-        <v>8</v>
+        <v>6.8</v>
       </c>
       <c r="N12" t="n">
-        <v>0.1720361466315535</v>
+        <v>0.148854616810747</v>
       </c>
       <c r="O12" t="n">
         <v>0.01199096286142609</v>
@@ -1183,7 +1183,7 @@
         <v>17.1993335323565</v>
       </c>
       <c r="K13" t="n">
-        <v>21.11801242236025</v>
+        <v>20.98765432098765</v>
       </c>
       <c r="L13" t="n">
         <v>4</v>
@@ -1226,13 +1226,13 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="G14" t="n">
-        <v>1.330316098170085</v>
+        <v>1.255199854093324</v>
       </c>
       <c r="H14" t="n">
-        <v>3.325137035561665</v>
+        <v>3.297952272619971</v>
       </c>
       <c r="I14" t="n">
         <v>-4.66984504576325</v>
@@ -1241,16 +1241,16 @@
         <v>9.823783930802669</v>
       </c>
       <c r="K14" t="n">
-        <v>39.1304347826087</v>
+        <v>38.2716049382716</v>
       </c>
       <c r="L14" t="n">
         <v>5</v>
       </c>
       <c r="M14" t="n">
-        <v>12.6</v>
+        <v>12.4</v>
       </c>
       <c r="N14" t="n">
-        <v>0.1936187364696616</v>
+        <v>0.1784807312402021</v>
       </c>
       <c r="O14" t="n">
         <v>-0.03344483363254391</v>
@@ -1299,7 +1299,7 @@
         <v>7.74527627402691</v>
       </c>
       <c r="K15" t="n">
-        <v>19.87577639751553</v>
+        <v>19.75308641975309</v>
       </c>
       <c r="L15" t="n">
         <v>5</v>
@@ -1342,13 +1342,13 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="G16" t="n">
-        <v>1.625311119029094</v>
+        <v>1.521601763880777</v>
       </c>
       <c r="H16" t="n">
-        <v>3.533744786395032</v>
+        <v>3.465956836136336</v>
       </c>
       <c r="I16" t="n">
         <v>-4.02566524721569</v>
@@ -1357,16 +1357,16 @@
         <v>10.3641980528429</v>
       </c>
       <c r="K16" t="n">
-        <v>19.87577639751553</v>
+        <v>20.98765432098765</v>
       </c>
       <c r="L16" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M16" t="n">
-        <v>8</v>
+        <v>6.8</v>
       </c>
       <c r="N16" t="n">
-        <v>0.1470494763866638</v>
+        <v>0.1170543160003003</v>
       </c>
       <c r="O16" t="n">
         <v>-0.04025665247215693</v>
@@ -1415,7 +1415,7 @@
         <v>9.57292159347422</v>
       </c>
       <c r="K17" t="n">
-        <v>21.11801242236025</v>
+        <v>20.98765432098765</v>
       </c>
       <c r="L17" t="n">
         <v>4</v>
@@ -1458,13 +1458,13 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="G18" t="n">
-        <v>1.31890453902616</v>
+        <v>1.274342131833923</v>
       </c>
       <c r="H18" t="n">
-        <v>5.965080736960624</v>
+        <v>6.003194643687698</v>
       </c>
       <c r="I18" t="n">
         <v>-11.8320411519501</v>
@@ -1473,16 +1473,16 @@
         <v>21.6010537672175</v>
       </c>
       <c r="K18" t="n">
-        <v>39.1304347826087</v>
+        <v>38.2716049382716</v>
       </c>
       <c r="L18" t="n">
         <v>5</v>
       </c>
       <c r="M18" t="n">
-        <v>12.6</v>
+        <v>12.4</v>
       </c>
       <c r="N18" t="n">
-        <v>0.1767191829623444</v>
+        <v>0.1662917430822683</v>
       </c>
       <c r="O18" t="n">
         <v>-0.1283343741738839</v>
@@ -1531,7 +1531,7 @@
         <v>11.4844653113646</v>
       </c>
       <c r="K19" t="n">
-        <v>19.87577639751553</v>
+        <v>19.75308641975309</v>
       </c>
       <c r="L19" t="n">
         <v>5</v>
@@ -1574,34 +1574,34 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.2898397090529166</v>
+        <v>-0.7351575918528768</v>
       </c>
       <c r="H20" t="n">
-        <v>4.96319845720355</v>
+        <v>5.50938236908935</v>
       </c>
       <c r="I20" t="n">
-        <v>-10.2721026685739</v>
+        <v>-15.9270162165717</v>
       </c>
       <c r="J20" t="n">
         <v>9.63714932872772</v>
       </c>
       <c r="K20" t="n">
-        <v>19.87577639751553</v>
+        <v>20.98765432098765</v>
       </c>
       <c r="L20" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M20" t="n">
-        <v>8</v>
+        <v>6.8</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.03116627485805717</v>
+        <v>-0.05643978249866042</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.06800842190965262</v>
+        <v>-0.1575338130610734</v>
       </c>
       <c r="P20" t="n">
         <v>0.05045070008285246</v>
@@ -1647,7 +1647,7 @@
         <v>25.6080879391498</v>
       </c>
       <c r="K21" t="n">
-        <v>21.11801242236025</v>
+        <v>20.98765432098765</v>
       </c>
       <c r="L21" t="n">
         <v>4</v>
@@ -1690,13 +1690,13 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="G22" t="n">
-        <v>2.281315888815698</v>
+        <v>2.29098455622489</v>
       </c>
       <c r="H22" t="n">
-        <v>4.481934865700838</v>
+        <v>4.517860264604721</v>
       </c>
       <c r="I22" t="n">
         <v>-7.834552959385981</v>
@@ -1705,16 +1705,16 @@
         <v>14.7955721617363</v>
       </c>
       <c r="K22" t="n">
-        <v>39.1304347826087</v>
+        <v>38.2716049382716</v>
       </c>
       <c r="L22" t="n">
         <v>5</v>
       </c>
       <c r="M22" t="n">
-        <v>12.6</v>
+        <v>12.4</v>
       </c>
       <c r="N22" t="n">
-        <v>0.3551572469557611</v>
+        <v>0.3497317708204247</v>
       </c>
       <c r="O22" t="n">
         <v>-0.04384403286972716</v>
@@ -1763,7 +1763,7 @@
         <v>17.2630481734445</v>
       </c>
       <c r="K23" t="n">
-        <v>19.87577639751553</v>
+        <v>19.75308641975309</v>
       </c>
       <c r="L23" t="n">
         <v>5</v>
@@ -1806,13 +1806,13 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="G24" t="n">
-        <v>1.393820605559812</v>
+        <v>1.285715974596975</v>
       </c>
       <c r="H24" t="n">
-        <v>4.320176615602557</v>
+        <v>4.336984778091733</v>
       </c>
       <c r="I24" t="n">
         <v>-6.284878505113629</v>
@@ -1821,16 +1821,16 @@
         <v>9.959724493416481</v>
       </c>
       <c r="K24" t="n">
-        <v>19.87577639751553</v>
+        <v>20.98765432098765</v>
       </c>
       <c r="L24" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M24" t="n">
-        <v>8</v>
+        <v>6.8</v>
       </c>
       <c r="N24" t="n">
-        <v>0.1145461894759124</v>
+        <v>0.08950733909719655</v>
       </c>
       <c r="O24" t="n">
         <v>-0.03954617158273233</v>
@@ -1879,7 +1879,7 @@
         <v>12.5443599847335</v>
       </c>
       <c r="K25" t="n">
-        <v>21.11801242236025</v>
+        <v>20.98765432098765</v>
       </c>
       <c r="L25" t="n">
         <v>4</v>
@@ -1922,13 +1922,13 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="G26" t="n">
-        <v>1.59435067319945</v>
+        <v>1.591603206236816</v>
       </c>
       <c r="H26" t="n">
-        <v>3.374334864751869</v>
+        <v>3.401809869290509</v>
       </c>
       <c r="I26" t="n">
         <v>-4.70593736639751</v>
@@ -1937,16 +1937,16 @@
         <v>9.96890693734484</v>
       </c>
       <c r="K26" t="n">
-        <v>39.1304347826087</v>
+        <v>38.2716049382716</v>
       </c>
       <c r="L26" t="n">
         <v>5</v>
       </c>
       <c r="M26" t="n">
-        <v>12.6</v>
+        <v>12.4</v>
       </c>
       <c r="N26" t="n">
-        <v>0.2534689711025697</v>
+        <v>0.2492382914820463</v>
       </c>
       <c r="O26" t="n">
         <v>-0.03629388667361888</v>
@@ -1995,7 +1995,7 @@
         <v>8.86970753112975</v>
       </c>
       <c r="K27" t="n">
-        <v>19.87577639751553</v>
+        <v>19.75308641975309</v>
       </c>
       <c r="L27" t="n">
         <v>5</v>
@@ -2038,34 +2038,34 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="G28" t="n">
-        <v>1.295103719669084</v>
+        <v>0.8542954949666298</v>
       </c>
       <c r="H28" t="n">
-        <v>4.113988105060878</v>
+        <v>4.37064551921874</v>
       </c>
       <c r="I28" t="n">
-        <v>-5.925261460528279</v>
+        <v>-6.25513270553522</v>
       </c>
       <c r="J28" t="n">
         <v>7.651278631372289</v>
       </c>
       <c r="K28" t="n">
-        <v>19.87577639751553</v>
+        <v>20.98765432098765</v>
       </c>
       <c r="L28" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M28" t="n">
-        <v>8</v>
+        <v>6.8</v>
       </c>
       <c r="N28" t="n">
-        <v>0.1118078804779745</v>
+        <v>0.06542015793403295</v>
       </c>
       <c r="O28" t="n">
-        <v>-0.05925261460528275</v>
+        <v>-0.1201307322417331</v>
       </c>
       <c r="P28" t="n">
         <v>0.3681830232103689</v>
@@ -2111,7 +2111,7 @@
         <v>10.2757108623477</v>
       </c>
       <c r="K29" t="n">
-        <v>21.11801242236025</v>
+        <v>20.98765432098765</v>
       </c>
       <c r="L29" t="n">
         <v>4</v>
@@ -2154,13 +2154,13 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="G30" t="n">
-        <v>1.88979785231731</v>
+        <v>1.939399161532498</v>
       </c>
       <c r="H30" t="n">
-        <v>4.16788365469603</v>
+        <v>4.183119601461454</v>
       </c>
       <c r="I30" t="n">
         <v>-5.93862228897025</v>
@@ -2169,16 +2169,16 @@
         <v>13.5073547998131</v>
       </c>
       <c r="K30" t="n">
-        <v>39.1304347826087</v>
+        <v>38.2716049382716</v>
       </c>
       <c r="L30" t="n">
         <v>5</v>
       </c>
       <c r="M30" t="n">
-        <v>12.6</v>
+        <v>12.4</v>
       </c>
       <c r="N30" t="n">
-        <v>0.2823707548130373</v>
+        <v>0.2855275258317235</v>
       </c>
       <c r="O30" t="n">
         <v>-0.006648237576164506</v>
@@ -2227,7 +2227,7 @@
         <v>11.9900891508605</v>
       </c>
       <c r="K31" t="n">
-        <v>19.87577639751553</v>
+        <v>19.75308641975309</v>
       </c>
       <c r="L31" t="n">
         <v>5</v>
@@ -2270,31 +2270,31 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="G32" t="n">
-        <v>1.19882992694781</v>
+        <v>1.296326368946536</v>
       </c>
       <c r="H32" t="n">
-        <v>3.34580457472999</v>
+        <v>3.516832116866826</v>
       </c>
       <c r="I32" t="n">
         <v>-6.39395114876894</v>
       </c>
       <c r="J32" t="n">
-        <v>7.456744942287171</v>
+        <v>8.145404066105311</v>
       </c>
       <c r="K32" t="n">
-        <v>19.87577639751553</v>
+        <v>20.98765432098765</v>
       </c>
       <c r="L32" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M32" t="n">
-        <v>8</v>
+        <v>6.8</v>
       </c>
       <c r="N32" t="n">
-        <v>0.1019822481374335</v>
+        <v>0.09261454287436935</v>
       </c>
       <c r="O32" t="n">
         <v>-0.01684894838002426</v>
@@ -2343,7 +2343,7 @@
         <v>14.5269451461826</v>
       </c>
       <c r="K33" t="n">
-        <v>21.11801242236025</v>
+        <v>20.98765432098765</v>
       </c>
       <c r="L33" t="n">
         <v>4</v>
@@ -2386,13 +2386,13 @@
         </is>
       </c>
       <c r="F34" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="G34" t="n">
-        <v>2.043950641208566</v>
+        <v>2.093851115554846</v>
       </c>
       <c r="H34" t="n">
-        <v>4.251819175111586</v>
+        <v>4.267889535836972</v>
       </c>
       <c r="I34" t="n">
         <v>-9.03342228644261</v>
@@ -2401,16 +2401,16 @@
         <v>13.0963168927553</v>
       </c>
       <c r="K34" t="n">
-        <v>39.1304347826087</v>
+        <v>38.2716049382716</v>
       </c>
       <c r="L34" t="n">
         <v>5</v>
       </c>
       <c r="M34" t="n">
-        <v>12.6</v>
+        <v>12.4</v>
       </c>
       <c r="N34" t="n">
-        <v>0.2984125510387441</v>
+        <v>0.3013602524333251</v>
       </c>
       <c r="O34" t="n">
         <v>0.0376879500447278</v>
@@ -2459,7 +2459,7 @@
         <v>10.24694135888</v>
       </c>
       <c r="K35" t="n">
-        <v>19.87577639751553</v>
+        <v>19.75308641975309</v>
       </c>
       <c r="L35" t="n">
         <v>5</v>
@@ -2502,13 +2502,13 @@
         </is>
       </c>
       <c r="F36" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="G36" t="n">
-        <v>1.869785122719442</v>
+        <v>2.029911899528887</v>
       </c>
       <c r="H36" t="n">
-        <v>4.794769818150074</v>
+        <v>4.893011988614491</v>
       </c>
       <c r="I36" t="n">
         <v>-7.30568996040934</v>
@@ -2517,16 +2517,16 @@
         <v>11.138619523777</v>
       </c>
       <c r="K36" t="n">
-        <v>19.87577639751553</v>
+        <v>20.98765432098765</v>
       </c>
       <c r="L36" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M36" t="n">
-        <v>8</v>
+        <v>6.8</v>
       </c>
       <c r="N36" t="n">
-        <v>0.1591831069783845</v>
+        <v>0.1455015765697016</v>
       </c>
       <c r="O36" t="n">
         <v>0.005677846780164364</v>
@@ -2575,7 +2575,7 @@
         <v>11.8700581470654</v>
       </c>
       <c r="K37" t="n">
-        <v>21.11801242236025</v>
+        <v>20.98765432098765</v>
       </c>
       <c r="L37" t="n">
         <v>4</v>
@@ -2618,13 +2618,13 @@
         </is>
       </c>
       <c r="F38" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="G38" t="n">
-        <v>1.453965102335928</v>
+        <v>1.473376362221011</v>
       </c>
       <c r="H38" t="n">
-        <v>3.586631954839385</v>
+        <v>3.612573251183403</v>
       </c>
       <c r="I38" t="n">
         <v>-6.119052067979229</v>
@@ -2633,16 +2633,16 @@
         <v>10.2371026217823</v>
       </c>
       <c r="K38" t="n">
-        <v>39.1304347826087</v>
+        <v>38.2716049382716</v>
       </c>
       <c r="L38" t="n">
         <v>5</v>
       </c>
       <c r="M38" t="n">
-        <v>12.6</v>
+        <v>12.4</v>
       </c>
       <c r="N38" t="n">
-        <v>0.2167319629055521</v>
+        <v>0.2161631940696445</v>
       </c>
       <c r="O38" t="n">
         <v>-0.02919700639085454</v>
@@ -2691,7 +2691,7 @@
         <v>9.97010822270626</v>
       </c>
       <c r="K39" t="n">
-        <v>19.87577639751553</v>
+        <v>19.75308641975309</v>
       </c>
       <c r="L39" t="n">
         <v>5</v>
@@ -2734,13 +2734,13 @@
         </is>
       </c>
       <c r="F40" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="G40" t="n">
-        <v>1.02153172876278</v>
+        <v>0.8915243717915948</v>
       </c>
       <c r="H40" t="n">
-        <v>4.765584253269591</v>
+        <v>4.730679242531885</v>
       </c>
       <c r="I40" t="n">
         <v>-8.02838978821635</v>
@@ -2749,19 +2749,19 @@
         <v>11.7139405168735</v>
       </c>
       <c r="K40" t="n">
-        <v>19.87577639751553</v>
+        <v>20.98765432098765</v>
       </c>
       <c r="L40" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M40" t="n">
-        <v>8</v>
+        <v>6.8</v>
       </c>
       <c r="N40" t="n">
-        <v>0.07749074574956705</v>
+        <v>0.05701359303286968</v>
       </c>
       <c r="O40" t="n">
-        <v>-0.01596672450639058</v>
+        <v>-0.02489501783391979</v>
       </c>
       <c r="P40" t="n">
         <v>0.1654960460136041</v>
@@ -2807,7 +2807,7 @@
         <v>9.589243507641781</v>
       </c>
       <c r="K41" t="n">
-        <v>21.11801242236025</v>
+        <v>20.98765432098765</v>
       </c>
       <c r="L41" t="n">
         <v>4</v>
@@ -2850,13 +2850,13 @@
         </is>
       </c>
       <c r="F42" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="G42" t="n">
-        <v>1.129899417120397</v>
+        <v>1.033442711355242</v>
       </c>
       <c r="H42" t="n">
-        <v>4.053303579919326</v>
+        <v>4.070343018551587</v>
       </c>
       <c r="I42" t="n">
         <v>-8.10424767618815</v>
@@ -2865,22 +2865,22 @@
         <v>9.6248306252491</v>
       </c>
       <c r="K42" t="n">
-        <v>34.95145631067961</v>
+        <v>33.65384615384615</v>
       </c>
       <c r="L42" t="n">
         <v>3</v>
       </c>
       <c r="M42" t="n">
-        <v>12</v>
+        <v>11.66666666666667</v>
       </c>
       <c r="N42" t="n">
-        <v>0.1396401339150191</v>
+        <v>0.1210484640780234</v>
       </c>
       <c r="O42" t="n">
         <v>0.007551522381175291</v>
       </c>
       <c r="P42" t="n">
-        <v>0.2936011062148047</v>
+        <v>0.2378260967038175</v>
       </c>
     </row>
     <row r="43">
@@ -2923,7 +2923,7 @@
         <v>6.84469377692436</v>
       </c>
       <c r="K43" t="n">
-        <v>25.24271844660194</v>
+        <v>25</v>
       </c>
       <c r="L43" t="n">
         <v>4</v>
@@ -2966,34 +2966,34 @@
         </is>
       </c>
       <c r="F44" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="G44" t="n">
-        <v>1.702528360247953</v>
+        <v>1.079068656284822</v>
       </c>
       <c r="H44" t="n">
-        <v>3.188721976290391</v>
+        <v>3.306655305527381</v>
       </c>
       <c r="I44" t="n">
-        <v>-2.30677757088085</v>
+        <v>-3.81879077014958</v>
       </c>
       <c r="J44" t="n">
         <v>7.202297448723289</v>
       </c>
       <c r="K44" t="n">
-        <v>8.737864077669903</v>
+        <v>10.57692307692308</v>
       </c>
       <c r="L44" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M44" t="n">
-        <v>4.5</v>
+        <v>3.666666666666667</v>
       </c>
       <c r="N44" t="n">
-        <v>0.0819278281488276</v>
+        <v>0.04306198941126849</v>
       </c>
       <c r="O44" t="n">
-        <v>-0.02306777570880847</v>
+        <v>-0.03466968806384974</v>
       </c>
       <c r="P44" t="n">
         <v>0.1869234320064637</v>
@@ -3039,7 +3039,7 @@
         <v>7.360199774148531</v>
       </c>
       <c r="K45" t="n">
-        <v>31.06796116504854</v>
+        <v>30.76923076923077</v>
       </c>
       <c r="L45" t="n">
         <v>3</v>
@@ -3082,13 +3082,13 @@
         </is>
       </c>
       <c r="F46" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="G46" t="n">
-        <v>1.262625270001743</v>
+        <v>1.253244686663834</v>
       </c>
       <c r="H46" t="n">
-        <v>4.406114392718932</v>
+        <v>4.441448997007622</v>
       </c>
       <c r="I46" t="n">
         <v>-7.088565609126809</v>
@@ -3097,16 +3097,16 @@
         <v>12.2158962489732</v>
       </c>
       <c r="K46" t="n">
-        <v>39.1304347826087</v>
+        <v>38.2716049382716</v>
       </c>
       <c r="L46" t="n">
         <v>5</v>
       </c>
       <c r="M46" t="n">
-        <v>12.6</v>
+        <v>12.4</v>
       </c>
       <c r="N46" t="n">
-        <v>0.1723852192576477</v>
+        <v>0.1674438087671844</v>
       </c>
       <c r="O46" t="n">
         <v>-0.0430587583608022</v>
@@ -3155,7 +3155,7 @@
         <v>7.714682238485699</v>
       </c>
       <c r="K47" t="n">
-        <v>19.87577639751553</v>
+        <v>19.75308641975309</v>
       </c>
       <c r="L47" t="n">
         <v>5</v>
@@ -3198,13 +3198,13 @@
         </is>
       </c>
       <c r="F48" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="G48" t="n">
-        <v>1.554108407035604</v>
+        <v>1.479291225980566</v>
       </c>
       <c r="H48" t="n">
-        <v>4.662304362634844</v>
+        <v>4.581673893450299</v>
       </c>
       <c r="I48" t="n">
         <v>-8.18149875021855</v>
@@ -3213,16 +3213,16 @@
         <v>10.9879016302789</v>
       </c>
       <c r="K48" t="n">
-        <v>19.87577639751553</v>
+        <v>20.98765432098765</v>
       </c>
       <c r="L48" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M48" t="n">
-        <v>8</v>
+        <v>6.8</v>
       </c>
       <c r="N48" t="n">
-        <v>0.1404570841757712</v>
+        <v>0.1133377992206024</v>
       </c>
       <c r="O48" t="n">
         <v>-0.08181498750218552</v>
@@ -3271,7 +3271,7 @@
         <v>6.83944264356443</v>
       </c>
       <c r="K49" t="n">
-        <v>21.11801242236025</v>
+        <v>20.98765432098765</v>
       </c>
       <c r="L49" t="n">
         <v>4</v>
@@ -3314,37 +3314,37 @@
         </is>
       </c>
       <c r="F50" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="G50" t="n">
-        <v>1.308689114876782</v>
+        <v>1.542439071048227</v>
       </c>
       <c r="H50" t="n">
-        <v>3.55134634593727</v>
+        <v>3.24235854617211</v>
       </c>
       <c r="I50" t="n">
-        <v>-8.508809044323931</v>
+        <v>-5.54358074682365</v>
       </c>
       <c r="J50" t="n">
         <v>6.95169290448147</v>
       </c>
       <c r="K50" t="n">
-        <v>33.07692307692307</v>
+        <v>32.06106870229007</v>
       </c>
       <c r="L50" t="n">
         <v>5</v>
       </c>
       <c r="M50" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="N50" t="n">
-        <v>0.1184859468952383</v>
+        <v>0.1423933908336546</v>
       </c>
       <c r="O50" t="n">
         <v>-0.02750881203672606</v>
       </c>
       <c r="P50" t="n">
-        <v>0.2853270694157186</v>
+        <v>0.4048642891078003</v>
       </c>
     </row>
     <row r="51">
@@ -3387,7 +3387,7 @@
         <v>7.285268265153571</v>
       </c>
       <c r="K51" t="n">
-        <v>20</v>
+        <v>19.84732824427481</v>
       </c>
       <c r="L51" t="n">
         <v>4</v>
@@ -3430,13 +3430,13 @@
         </is>
       </c>
       <c r="F52" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="G52" t="n">
-        <v>1.175958538244241</v>
+        <v>1.189292861681597</v>
       </c>
       <c r="H52" t="n">
-        <v>3.766958823644031</v>
+        <v>3.803673103524818</v>
       </c>
       <c r="I52" t="n">
         <v>-6.986148218179911</v>
@@ -3445,16 +3445,16 @@
         <v>7.521483003263831</v>
       </c>
       <c r="K52" t="n">
-        <v>22.30769230769231</v>
+        <v>23.66412213740458</v>
       </c>
       <c r="L52" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M52" t="n">
-        <v>9.666666666666666</v>
+        <v>7.75</v>
       </c>
       <c r="N52" t="n">
-        <v>0.1198467378950679</v>
+        <v>0.0963880667567612</v>
       </c>
       <c r="O52" t="n">
         <v>-0.03198909559765961</v>
@@ -3503,7 +3503,7 @@
         <v>8.975974874825891</v>
       </c>
       <c r="K53" t="n">
-        <v>24.61538461538462</v>
+        <v>24.42748091603053</v>
       </c>
       <c r="L53" t="n">
         <v>3</v>
@@ -3546,37 +3546,37 @@
         </is>
       </c>
       <c r="F54" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="G54" t="n">
-        <v>1.224987196284963</v>
+        <v>1.480901384204729</v>
       </c>
       <c r="H54" t="n">
-        <v>3.648646427811727</v>
+        <v>3.279096359932725</v>
       </c>
       <c r="I54" t="n">
-        <v>-9.523408696345211</v>
+        <v>-5.82279192050039</v>
       </c>
       <c r="J54" t="n">
         <v>7.6716417531022</v>
       </c>
       <c r="K54" t="n">
-        <v>33.07692307692307</v>
+        <v>32.06106870229007</v>
       </c>
       <c r="L54" t="n">
         <v>5</v>
       </c>
       <c r="M54" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="N54" t="n">
-        <v>0.1081754616665886</v>
+        <v>0.1339981301961045</v>
       </c>
       <c r="O54" t="n">
         <v>-0.02026323853882039</v>
       </c>
       <c r="P54" t="n">
-        <v>0.2266338143249953</v>
+        <v>0.3557471569725745</v>
       </c>
     </row>
     <row r="55">
@@ -3619,7 +3619,7 @@
         <v>6.94715275176028</v>
       </c>
       <c r="K55" t="n">
-        <v>20</v>
+        <v>19.84732824427481</v>
       </c>
       <c r="L55" t="n">
         <v>4</v>
@@ -3662,13 +3662,13 @@
         </is>
       </c>
       <c r="F56" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="G56" t="n">
-        <v>1.326948059546001</v>
+        <v>1.319659665550913</v>
       </c>
       <c r="H56" t="n">
-        <v>3.379239678469683</v>
+        <v>3.505195498158436</v>
       </c>
       <c r="I56" t="n">
         <v>-5.24453965145917</v>
@@ -3677,16 +3677,16 @@
         <v>7.13073476203116</v>
       </c>
       <c r="K56" t="n">
-        <v>22.30769230769231</v>
+        <v>23.66412213740458</v>
       </c>
       <c r="L56" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M56" t="n">
-        <v>9.666666666666666</v>
+        <v>7.75</v>
       </c>
       <c r="N56" t="n">
-        <v>0.1381218122909311</v>
+        <v>0.1090877339913797</v>
       </c>
       <c r="O56" t="n">
         <v>-0.01628597000901144</v>
@@ -3735,7 +3735,7 @@
         <v>7.925364439758551</v>
       </c>
       <c r="K57" t="n">
-        <v>24.61538461538462</v>
+        <v>24.42748091603053</v>
       </c>
       <c r="L57" t="n">
         <v>3</v>
@@ -3778,37 +3778,37 @@
         </is>
       </c>
       <c r="F58" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="G58" t="n">
-        <v>1.121544945711472</v>
+        <v>1.351951188266407</v>
       </c>
       <c r="H58" t="n">
-        <v>3.561807350733982</v>
+        <v>3.264579378436513</v>
       </c>
       <c r="I58" t="n">
-        <v>-8.555517241595799</v>
+        <v>-4.41020346327878</v>
       </c>
       <c r="J58" t="n">
         <v>7.36666934510836</v>
       </c>
       <c r="K58" t="n">
-        <v>33.07692307692307</v>
+        <v>32.06106870229007</v>
       </c>
       <c r="L58" t="n">
         <v>5</v>
       </c>
       <c r="M58" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="N58" t="n">
-        <v>0.09954799099203782</v>
+        <v>0.1237357192886825</v>
       </c>
       <c r="O58" t="n">
         <v>-0.01152848052935629</v>
       </c>
       <c r="P58" t="n">
-        <v>0.2926362256824393</v>
+        <v>0.4135748671656625</v>
       </c>
     </row>
     <row r="59">
@@ -3851,7 +3851,7 @@
         <v>7.93887645673724</v>
       </c>
       <c r="K59" t="n">
-        <v>20</v>
+        <v>19.84732824427481</v>
       </c>
       <c r="L59" t="n">
         <v>4</v>
@@ -3894,13 +3894,13 @@
         </is>
       </c>
       <c r="F60" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="G60" t="n">
-        <v>1.835752584812977</v>
+        <v>1.667960216688404</v>
       </c>
       <c r="H60" t="n">
-        <v>3.42028933546584</v>
+        <v>3.4523374434225</v>
       </c>
       <c r="I60" t="n">
         <v>-4.57958033380678</v>
@@ -3909,16 +3909,16 @@
         <v>8.375876401854281</v>
       </c>
       <c r="K60" t="n">
-        <v>22.30769230769231</v>
+        <v>23.66412213740458</v>
       </c>
       <c r="L60" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M60" t="n">
-        <v>9.666666666666666</v>
+        <v>7.75</v>
       </c>
       <c r="N60" t="n">
-        <v>0.2022222562101833</v>
+        <v>0.1476393151596483</v>
       </c>
       <c r="O60" t="n">
         <v>-0.04579580333806776</v>
@@ -3967,7 +3967,7 @@
         <v>6.87229435690348</v>
       </c>
       <c r="K61" t="n">
-        <v>24.61538461538462</v>
+        <v>24.42748091603053</v>
       </c>
       <c r="L61" t="n">
         <v>3</v>
@@ -4010,37 +4010,37 @@
         </is>
       </c>
       <c r="F62" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="G62" t="n">
-        <v>1.376336791123065</v>
+        <v>1.674763436267108</v>
       </c>
       <c r="H62" t="n">
-        <v>3.743228803862341</v>
+        <v>3.229643246726068</v>
       </c>
       <c r="I62" t="n">
-        <v>-11.1575823049267</v>
+        <v>-5.997547424664449</v>
       </c>
       <c r="J62" t="n">
         <v>6.89263768827785</v>
       </c>
       <c r="K62" t="n">
-        <v>33.07692307692307</v>
+        <v>32.06106870229007</v>
       </c>
       <c r="L62" t="n">
         <v>5</v>
       </c>
       <c r="M62" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="N62" t="n">
-        <v>0.1233762685115819</v>
+        <v>0.1548793911144378</v>
       </c>
       <c r="O62" t="n">
         <v>-0.01208145336572686</v>
       </c>
       <c r="P62" t="n">
-        <v>0.2542204487015984</v>
+        <v>0.4117360617158783</v>
       </c>
     </row>
     <row r="63">
@@ -4083,7 +4083,7 @@
         <v>7.2021582714579</v>
       </c>
       <c r="K63" t="n">
-        <v>20</v>
+        <v>19.84732824427481</v>
       </c>
       <c r="L63" t="n">
         <v>4</v>
@@ -4126,13 +4126,13 @@
         </is>
       </c>
       <c r="F64" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="G64" t="n">
-        <v>1.369305528832231</v>
+        <v>1.367730661845499</v>
       </c>
       <c r="H64" t="n">
-        <v>3.4098884649252</v>
+        <v>3.509497511236934</v>
       </c>
       <c r="I64" t="n">
         <v>-5.23417007004207</v>
@@ -4141,16 +4141,16 @@
         <v>7.17869308850433</v>
       </c>
       <c r="K64" t="n">
-        <v>22.30769230769231</v>
+        <v>23.66412213740458</v>
       </c>
       <c r="L64" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M64" t="n">
-        <v>9.666666666666666</v>
+        <v>7.75</v>
       </c>
       <c r="N64" t="n">
-        <v>0.1425779314679243</v>
+        <v>0.1131540105365176</v>
       </c>
       <c r="O64" t="n">
         <v>-0.01636330309291345</v>
@@ -4199,7 +4199,7 @@
         <v>8.24611022911178</v>
       </c>
       <c r="K65" t="n">
-        <v>24.61538461538462</v>
+        <v>24.42748091603053</v>
       </c>
       <c r="L65" t="n">
         <v>3</v>
@@ -4242,37 +4242,37 @@
         </is>
       </c>
       <c r="F66" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G66" t="n">
-        <v>1.581408455357284</v>
+        <v>1.852079742450122</v>
       </c>
       <c r="H66" t="n">
-        <v>4.393631911096492</v>
+        <v>3.93481658177471</v>
       </c>
       <c r="I66" t="n">
-        <v>-13.3055123347488</v>
+        <v>-6.747234236335339</v>
       </c>
       <c r="J66" t="n">
         <v>11.7483945325047</v>
       </c>
       <c r="K66" t="n">
-        <v>39.16083916083916</v>
+        <v>38.19444444444444</v>
       </c>
       <c r="L66" t="n">
         <v>5</v>
       </c>
       <c r="M66" t="n">
-        <v>11.2</v>
+        <v>11</v>
       </c>
       <c r="N66" t="n">
-        <v>0.1888311571191753</v>
+        <v>0.2290583342417606</v>
       </c>
       <c r="O66" t="n">
         <v>-0.01023538750965192</v>
       </c>
       <c r="P66" t="n">
-        <v>0.3928046843520732</v>
+        <v>0.5116733617813327</v>
       </c>
     </row>
     <row r="67">
@@ -4315,7 +4315,7 @@
         <v>7.42189952260202</v>
       </c>
       <c r="K67" t="n">
-        <v>18.18181818181818</v>
+        <v>18.05555555555555</v>
       </c>
       <c r="L67" t="n">
         <v>4</v>
@@ -4358,13 +4358,13 @@
         </is>
       </c>
       <c r="F68" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="G68" t="n">
-        <v>1.687372750365663</v>
+        <v>1.82486140770451</v>
       </c>
       <c r="H68" t="n">
-        <v>3.437242761125542</v>
+        <v>3.513377893690257</v>
       </c>
       <c r="I68" t="n">
         <v>-3.99764824263489</v>
@@ -4373,16 +4373,16 @@
         <v>8.541253775102129</v>
       </c>
       <c r="K68" t="n">
-        <v>20.27972027972028</v>
+        <v>21.52777777777778</v>
       </c>
       <c r="L68" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M68" t="n">
-        <v>9.666666666666666</v>
+        <v>7.75</v>
       </c>
       <c r="N68" t="n">
-        <v>0.1805679689317985</v>
+        <v>0.1544951259325026</v>
       </c>
       <c r="O68" t="n">
         <v>0.005915057912824206</v>
@@ -4431,7 +4431,7 @@
         <v>13.1224591254952</v>
       </c>
       <c r="K69" t="n">
-        <v>22.37762237762238</v>
+        <v>22.22222222222222</v>
       </c>
       <c r="L69" t="n">
         <v>3</v>
@@ -4474,37 +4474,37 @@
         </is>
       </c>
       <c r="F70" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G70" t="n">
-        <v>1.374051827623967</v>
+        <v>1.611249289018029</v>
       </c>
       <c r="H70" t="n">
-        <v>3.758934545501023</v>
+        <v>3.343978758250776</v>
       </c>
       <c r="I70" t="n">
-        <v>-11.6718085490494</v>
+        <v>-6.02684421181042</v>
       </c>
       <c r="J70" t="n">
         <v>8.538804320682219</v>
       </c>
       <c r="K70" t="n">
-        <v>39.16083916083916</v>
+        <v>38.19444444444444</v>
       </c>
       <c r="L70" t="n">
         <v>5</v>
       </c>
       <c r="M70" t="n">
-        <v>11.2</v>
+        <v>11</v>
       </c>
       <c r="N70" t="n">
-        <v>0.1627384891323143</v>
+        <v>0.1956956467076387</v>
       </c>
       <c r="O70" t="n">
         <v>-0.01060235851672997</v>
       </c>
       <c r="P70" t="n">
-        <v>0.337710289520283</v>
+        <v>0.4118273717747234</v>
       </c>
     </row>
     <row r="71">
@@ -4547,7 +4547,7 @@
         <v>8.076570009882129</v>
       </c>
       <c r="K71" t="n">
-        <v>18.18181818181818</v>
+        <v>18.05555555555555</v>
       </c>
       <c r="L71" t="n">
         <v>4</v>
@@ -4590,13 +4590,13 @@
         </is>
       </c>
       <c r="F72" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="G72" t="n">
-        <v>1.590597167171194</v>
+        <v>1.521348415428735</v>
       </c>
       <c r="H72" t="n">
-        <v>3.574127644068584</v>
+        <v>3.570036812116642</v>
       </c>
       <c r="I72" t="n">
         <v>-5.34515385225228</v>
@@ -4605,16 +4605,16 @@
         <v>7.72617150656165</v>
       </c>
       <c r="K72" t="n">
-        <v>20.27972027972028</v>
+        <v>21.52777777777778</v>
       </c>
       <c r="L72" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M72" t="n">
-        <v>9.666666666666666</v>
+        <v>7.75</v>
       </c>
       <c r="N72" t="n">
-        <v>0.168857882981481</v>
+        <v>0.1289548522576497</v>
       </c>
       <c r="O72" t="n">
         <v>-0.02496366494041635</v>
@@ -4663,7 +4663,7 @@
         <v>7.69497967124499</v>
       </c>
       <c r="K73" t="n">
-        <v>22.37762237762238</v>
+        <v>22.22222222222222</v>
       </c>
       <c r="L73" t="n">
         <v>3</v>
@@ -4706,37 +4706,37 @@
         </is>
       </c>
       <c r="F74" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="G74" t="n">
-        <v>1.180255717123087</v>
+        <v>1.427856165170456</v>
       </c>
       <c r="H74" t="n">
-        <v>3.648201252015532</v>
+        <v>3.338090341682212</v>
       </c>
       <c r="I74" t="n">
-        <v>-8.47616175672427</v>
+        <v>-4.88900426378396</v>
       </c>
       <c r="J74" t="n">
         <v>7.79885715856029</v>
       </c>
       <c r="K74" t="n">
-        <v>32.25806451612903</v>
+        <v>31.2</v>
       </c>
       <c r="L74" t="n">
         <v>4</v>
       </c>
       <c r="M74" t="n">
-        <v>10</v>
+        <v>9.75</v>
       </c>
       <c r="N74" t="n">
-        <v>0.123231555519747</v>
+        <v>0.1514102785121009</v>
       </c>
       <c r="O74" t="n">
         <v>-0.0119688944570685</v>
       </c>
       <c r="P74" t="n">
-        <v>0.2556739569809678</v>
+        <v>0.3297869389997989</v>
       </c>
     </row>
     <row r="75">
@@ -4779,7 +4779,7 @@
         <v>7.56280518804586</v>
       </c>
       <c r="K75" t="n">
-        <v>20.96774193548387</v>
+        <v>20.8</v>
       </c>
       <c r="L75" t="n">
         <v>4</v>
@@ -4822,13 +4822,13 @@
         </is>
       </c>
       <c r="F76" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="G76" t="n">
-        <v>0.9444858044822287</v>
+        <v>0.8952174699847264</v>
       </c>
       <c r="H76" t="n">
-        <v>3.447811897628859</v>
+        <v>3.505631342934171</v>
       </c>
       <c r="I76" t="n">
         <v>-4.962450921223549</v>
@@ -4837,16 +4837,16 @@
         <v>6.989405251611849</v>
       </c>
       <c r="K76" t="n">
-        <v>20.96774193548387</v>
+        <v>22.4</v>
       </c>
       <c r="L76" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M76" t="n">
-        <v>8.666666666666666</v>
+        <v>7</v>
       </c>
       <c r="N76" t="n">
-        <v>0.08239529263763223</v>
+        <v>0.06264990668686923</v>
       </c>
       <c r="O76" t="n">
         <v>-0.02210359171009768</v>
@@ -4895,7 +4895,7 @@
         <v>9.52544316828399</v>
       </c>
       <c r="K77" t="n">
-        <v>25.80645161290322</v>
+        <v>25.6</v>
       </c>
       <c r="L77" t="n">
         <v>3</v>
@@ -4911,9 +4911,1224 @@
       </c>
       <c r="P77" t="n">
         <v>0.1048620471285071</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="1" t="n">
+        <v>76</v>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>Commodities</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>Type 1</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>Type 1: Strengthening CLI &amp; Falling Inflation</t>
+        </is>
+      </c>
+      <c r="F78" t="n">
+        <v>124</v>
+      </c>
+      <c r="G78" t="n">
+        <v>0.6797013860230806</v>
+      </c>
+      <c r="H78" t="n">
+        <v>3.224069697337324</v>
+      </c>
+      <c r="I78" t="n">
+        <v>-7.181241138839139</v>
+      </c>
+      <c r="J78" t="n">
+        <v>8.424126327671139</v>
+      </c>
+      <c r="K78" t="n">
+        <v>33.97260273972603</v>
+      </c>
+      <c r="L78" t="n">
+        <v>13</v>
+      </c>
+      <c r="M78" t="n">
+        <v>9.538461538461538</v>
+      </c>
+      <c r="N78" t="n">
+        <v>0.06673588292886144</v>
+      </c>
+      <c r="O78" t="n">
+        <v>-0.05230092059847635</v>
+      </c>
+      <c r="P78" t="n">
+        <v>0.2403869557370633</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="1" t="n">
+        <v>77</v>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>Commodities</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>Type 2</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>Type 2: Strengthening CLI &amp; Rising Inflation</t>
+        </is>
+      </c>
+      <c r="F79" t="n">
+        <v>68</v>
+      </c>
+      <c r="G79" t="n">
+        <v>0.803856887670368</v>
+      </c>
+      <c r="H79" t="n">
+        <v>3.147015475365903</v>
+      </c>
+      <c r="I79" t="n">
+        <v>-8.15079939713149</v>
+      </c>
+      <c r="J79" t="n">
+        <v>8.82228163422023</v>
+      </c>
+      <c r="K79" t="n">
+        <v>18.63013698630137</v>
+      </c>
+      <c r="L79" t="n">
+        <v>12</v>
+      </c>
+      <c r="M79" t="n">
+        <v>5.666666666666667</v>
+      </c>
+      <c r="N79" t="n">
+        <v>0.04769233801660385</v>
+      </c>
+      <c r="O79" t="n">
+        <v>-0.08150799397131492</v>
+      </c>
+      <c r="P79" t="n">
+        <v>0.2189090134562799</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="1" t="n">
+        <v>78</v>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>Commodities</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>Type 3</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>Type 3: Weakening CLI &amp; Falling Inflation</t>
+        </is>
+      </c>
+      <c r="F80" t="n">
+        <v>77</v>
+      </c>
+      <c r="G80" t="n">
+        <v>-0.2578925309576527</v>
+      </c>
+      <c r="H80" t="n">
+        <v>3.572345026311512</v>
+      </c>
+      <c r="I80" t="n">
+        <v>-8.681400900200641</v>
+      </c>
+      <c r="J80" t="n">
+        <v>9.379507611538331</v>
+      </c>
+      <c r="K80" t="n">
+        <v>21.0958904109589</v>
+      </c>
+      <c r="L80" t="n">
+        <v>14</v>
+      </c>
+      <c r="M80" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="N80" t="n">
+        <v>-0.01357023766335624</v>
+      </c>
+      <c r="O80" t="n">
+        <v>-0.2172697385455662</v>
+      </c>
+      <c r="P80" t="n">
+        <v>0.1108537781755881</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="1" t="n">
+        <v>79</v>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>Commodities</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>Type 4</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>Type 4: Weakening CLI &amp; Rising Inflation</t>
+        </is>
+      </c>
+      <c r="F81" t="n">
+        <v>96</v>
+      </c>
+      <c r="G81" t="n">
+        <v>0.01652860430339861</v>
+      </c>
+      <c r="H81" t="n">
+        <v>4.35451013161507</v>
+      </c>
+      <c r="I81" t="n">
+        <v>-10.7859098091527</v>
+      </c>
+      <c r="J81" t="n">
+        <v>12.2526415215383</v>
+      </c>
+      <c r="K81" t="n">
+        <v>26.3013698630137</v>
+      </c>
+      <c r="L81" t="n">
+        <v>12</v>
+      </c>
+      <c r="M81" t="n">
+        <v>8</v>
+      </c>
+      <c r="N81" t="n">
+        <v>-5.105537682339086e-05</v>
+      </c>
+      <c r="O81" t="n">
+        <v>-0.1895693433080879</v>
+      </c>
+      <c r="P81" t="n">
+        <v>0.2190139872221295</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="1" t="n">
+        <v>80</v>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>Global_Agg_Hedged</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>Type 1</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>Type 1: Strengthening CLI &amp; Falling Inflation</t>
+        </is>
+      </c>
+      <c r="F82" t="n">
+        <v>124</v>
+      </c>
+      <c r="G82" t="n">
+        <v>0.3828144628263419</v>
+      </c>
+      <c r="H82" t="n">
+        <v>0.9599538932805715</v>
+      </c>
+      <c r="I82" t="n">
+        <v>-1.84891564322378</v>
+      </c>
+      <c r="J82" t="n">
+        <v>3.20100406514402</v>
+      </c>
+      <c r="K82" t="n">
+        <v>33.97260273972603</v>
+      </c>
+      <c r="L82" t="n">
+        <v>13</v>
+      </c>
+      <c r="M82" t="n">
+        <v>9.538461538461538</v>
+      </c>
+      <c r="N82" t="n">
+        <v>0.03726867862913498</v>
+      </c>
+      <c r="O82" t="n">
+        <v>-0.008573258647496917</v>
+      </c>
+      <c r="P82" t="n">
+        <v>0.1088088975691219</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="1" t="n">
+        <v>81</v>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>Global_Agg_Hedged</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>Type 2</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>Type 2: Strengthening CLI &amp; Rising Inflation</t>
+        </is>
+      </c>
+      <c r="F83" t="n">
+        <v>68</v>
+      </c>
+      <c r="G83" t="n">
+        <v>0.4466881618778629</v>
+      </c>
+      <c r="H83" t="n">
+        <v>0.8121691204539814</v>
+      </c>
+      <c r="I83" t="n">
+        <v>-1.7201545591908</v>
+      </c>
+      <c r="J83" t="n">
+        <v>2.10200029059912</v>
+      </c>
+      <c r="K83" t="n">
+        <v>18.63013698630137</v>
+      </c>
+      <c r="L83" t="n">
+        <v>12</v>
+      </c>
+      <c r="M83" t="n">
+        <v>5.666666666666667</v>
+      </c>
+      <c r="N83" t="n">
+        <v>0.02592614372646551</v>
+      </c>
+      <c r="O83" t="n">
+        <v>-0.01720154559190801</v>
+      </c>
+      <c r="P83" t="n">
+        <v>0.1168753726893259</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="1" t="n">
+        <v>82</v>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>Global_Agg_Hedged</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>Type 3</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>Type 3: Weakening CLI &amp; Falling Inflation</t>
+        </is>
+      </c>
+      <c r="F84" t="n">
+        <v>77</v>
+      </c>
+      <c r="G84" t="n">
+        <v>0.8090197869101518</v>
+      </c>
+      <c r="H84" t="n">
+        <v>0.8336950578304456</v>
+      </c>
+      <c r="I84" t="n">
+        <v>-1.06770592199458</v>
+      </c>
+      <c r="J84" t="n">
+        <v>3.69680550852241</v>
+      </c>
+      <c r="K84" t="n">
+        <v>21.0958904109589</v>
+      </c>
+      <c r="L84" t="n">
+        <v>14</v>
+      </c>
+      <c r="M84" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="N84" t="n">
+        <v>0.04593349216771875</v>
+      </c>
+      <c r="O84" t="n">
+        <v>-0.00650462170489563</v>
+      </c>
+      <c r="P84" t="n">
+        <v>0.1126273784204268</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="1" t="n">
+        <v>83</v>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>Global_Agg_Hedged</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>Type 4</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>Type 4: Weakening CLI &amp; Rising Inflation</t>
+        </is>
+      </c>
+      <c r="F85" t="n">
+        <v>96</v>
+      </c>
+      <c r="G85" t="n">
+        <v>0.4894460501086021</v>
+      </c>
+      <c r="H85" t="n">
+        <v>1.174993036132732</v>
+      </c>
+      <c r="I85" t="n">
+        <v>-3.49707228602284</v>
+      </c>
+      <c r="J85" t="n">
+        <v>3.04477020602219</v>
+      </c>
+      <c r="K85" t="n">
+        <v>26.3013698630137</v>
+      </c>
+      <c r="L85" t="n">
+        <v>12</v>
+      </c>
+      <c r="M85" t="n">
+        <v>8</v>
+      </c>
+      <c r="N85" t="n">
+        <v>0.04162929865908083</v>
+      </c>
+      <c r="O85" t="n">
+        <v>-0.1134775737481035</v>
+      </c>
+      <c r="P85" t="n">
+        <v>0.1944165644399833</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="1" t="n">
+        <v>84</v>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>Global_Agg_IGCredit_Hedged</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>Type 1</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>Type 1: Strengthening CLI &amp; Falling Inflation</t>
+        </is>
+      </c>
+      <c r="F86" t="n">
+        <v>103</v>
+      </c>
+      <c r="G86" t="n">
+        <v>0.4890826331747369</v>
+      </c>
+      <c r="H86" t="n">
+        <v>1.228835199326766</v>
+      </c>
+      <c r="I86" t="n">
+        <v>-2.46847418568061</v>
+      </c>
+      <c r="J86" t="n">
+        <v>4.07926854837464</v>
+      </c>
+      <c r="K86" t="n">
+        <v>34.7972972972973</v>
+      </c>
+      <c r="L86" t="n">
+        <v>10</v>
+      </c>
+      <c r="M86" t="n">
+        <v>10.3</v>
+      </c>
+      <c r="N86" t="n">
+        <v>0.05164701793971523</v>
+      </c>
+      <c r="O86" t="n">
+        <v>0.006721268502088762</v>
+      </c>
+      <c r="P86" t="n">
+        <v>0.147091697954961</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="1" t="n">
+        <v>85</v>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>Global_Agg_IGCredit_Hedged</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>Type 2</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>Type 2: Strengthening CLI &amp; Rising Inflation</t>
+        </is>
+      </c>
+      <c r="F87" t="n">
+        <v>51</v>
+      </c>
+      <c r="G87" t="n">
+        <v>0.3478355982808841</v>
+      </c>
+      <c r="H87" t="n">
+        <v>1.318300353850228</v>
+      </c>
+      <c r="I87" t="n">
+        <v>-6.44907253014457</v>
+      </c>
+      <c r="J87" t="n">
+        <v>2.65425684189646</v>
+      </c>
+      <c r="K87" t="n">
+        <v>17.22972972972973</v>
+      </c>
+      <c r="L87" t="n">
+        <v>10</v>
+      </c>
+      <c r="M87" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="N87" t="n">
+        <v>0.01803489277066922</v>
+      </c>
+      <c r="O87" t="n">
+        <v>-0.06449072530144573</v>
+      </c>
+      <c r="P87" t="n">
+        <v>0.08551682069112765</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="1" t="n">
+        <v>86</v>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>Global_Agg_IGCredit_Hedged</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>Type 3</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>Type 3: Weakening CLI &amp; Falling Inflation</t>
+        </is>
+      </c>
+      <c r="F88" t="n">
+        <v>57</v>
+      </c>
+      <c r="G88" t="n">
+        <v>0.7738529166745778</v>
+      </c>
+      <c r="H88" t="n">
+        <v>0.94316923006219</v>
+      </c>
+      <c r="I88" t="n">
+        <v>-1.48836194752197</v>
+      </c>
+      <c r="J88" t="n">
+        <v>2.70357383659126</v>
+      </c>
+      <c r="K88" t="n">
+        <v>19.25675675675676</v>
+      </c>
+      <c r="L88" t="n">
+        <v>11</v>
+      </c>
+      <c r="M88" t="n">
+        <v>5.181818181818182</v>
+      </c>
+      <c r="N88" t="n">
+        <v>0.04116544808963199</v>
+      </c>
+      <c r="O88" t="n">
+        <v>-0.003616191384241962</v>
+      </c>
+      <c r="P88" t="n">
+        <v>0.1084337451252413</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="1" t="n">
+        <v>87</v>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>Global_Agg_IGCredit_Hedged</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>Type 4</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>Type 4: Weakening CLI &amp; Rising Inflation</t>
+        </is>
+      </c>
+      <c r="F89" t="n">
+        <v>85</v>
+      </c>
+      <c r="G89" t="n">
+        <v>0.3614617524430354</v>
+      </c>
+      <c r="H89" t="n">
+        <v>1.781873226666296</v>
+      </c>
+      <c r="I89" t="n">
+        <v>-4.88462964234228</v>
+      </c>
+      <c r="J89" t="n">
+        <v>3.89681829021909</v>
+      </c>
+      <c r="K89" t="n">
+        <v>28.71621621621622</v>
+      </c>
+      <c r="L89" t="n">
+        <v>11</v>
+      </c>
+      <c r="M89" t="n">
+        <v>7.727272727272728</v>
+      </c>
+      <c r="N89" t="n">
+        <v>0.02952088676571334</v>
+      </c>
+      <c r="O89" t="n">
+        <v>-0.147781177049898</v>
+      </c>
+      <c r="P89" t="n">
+        <v>0.1430411413568475</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="1" t="n">
+        <v>88</v>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>Global_Agg_HYCredit_Hedged</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>Type 1</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>Type 1: Strengthening CLI &amp; Falling Inflation</t>
+        </is>
+      </c>
+      <c r="F90" t="n">
+        <v>101</v>
+      </c>
+      <c r="G90" t="n">
+        <v>0.9439149689520268</v>
+      </c>
+      <c r="H90" t="n">
+        <v>1.769106171540513</v>
+      </c>
+      <c r="I90" t="n">
+        <v>-6.929464541376349</v>
+      </c>
+      <c r="J90" t="n">
+        <v>6.0219237887344</v>
+      </c>
+      <c r="K90" t="n">
+        <v>36.07142857142857</v>
+      </c>
+      <c r="L90" t="n">
+        <v>10</v>
+      </c>
+      <c r="M90" t="n">
+        <v>10.1</v>
+      </c>
+      <c r="N90" t="n">
+        <v>0.1020296187396682</v>
+      </c>
+      <c r="O90" t="n">
+        <v>-0.03760363205684969</v>
+      </c>
+      <c r="P90" t="n">
+        <v>0.3013811918262546</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="1" t="n">
+        <v>89</v>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>Global_Agg_HYCredit_Hedged</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>Type 2</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>Type 2: Strengthening CLI &amp; Rising Inflation</t>
+        </is>
+      </c>
+      <c r="F91" t="n">
+        <v>51</v>
+      </c>
+      <c r="G91" t="n">
+        <v>0.5380013690371759</v>
+      </c>
+      <c r="H91" t="n">
+        <v>2.527208857349815</v>
+      </c>
+      <c r="I91" t="n">
+        <v>-14.2692493185119</v>
+      </c>
+      <c r="J91" t="n">
+        <v>3.85016947536215</v>
+      </c>
+      <c r="K91" t="n">
+        <v>18.21428571428571</v>
+      </c>
+      <c r="L91" t="n">
+        <v>10</v>
+      </c>
+      <c r="M91" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="N91" t="n">
+        <v>0.02808474580443963</v>
+      </c>
+      <c r="O91" t="n">
+        <v>-0.142692493185119</v>
+      </c>
+      <c r="P91" t="n">
+        <v>0.1022352386723222</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="1" t="n">
+        <v>90</v>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>Global_Agg_HYCredit_Hedged</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>Type 3</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>Type 3: Weakening CLI &amp; Falling Inflation</t>
+        </is>
+      </c>
+      <c r="F92" t="n">
+        <v>56</v>
+      </c>
+      <c r="G92" t="n">
+        <v>1.301039889505502</v>
+      </c>
+      <c r="H92" t="n">
+        <v>2.601939850776264</v>
+      </c>
+      <c r="I92" t="n">
+        <v>-4.80976310122039</v>
+      </c>
+      <c r="J92" t="n">
+        <v>10.5353534010951</v>
+      </c>
+      <c r="K92" t="n">
+        <v>20</v>
+      </c>
+      <c r="L92" t="n">
+        <v>10</v>
+      </c>
+      <c r="M92" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="N92" t="n">
+        <v>0.0757621381929878</v>
+      </c>
+      <c r="O92" t="n">
+        <v>0.01614546001046779</v>
+      </c>
+      <c r="P92" t="n">
+        <v>0.2690805038576816</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="1" t="n">
+        <v>91</v>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>Global_Agg_HYCredit_Hedged</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>Type 4</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>Type 4: Weakening CLI &amp; Rising Inflation</t>
+        </is>
+      </c>
+      <c r="F93" t="n">
+        <v>72</v>
+      </c>
+      <c r="G93" t="n">
+        <v>0.1249276297288903</v>
+      </c>
+      <c r="H93" t="n">
+        <v>3.847411578439553</v>
+      </c>
+      <c r="I93" t="n">
+        <v>-21.0174744829797</v>
+      </c>
+      <c r="J93" t="n">
+        <v>6.57176964259876</v>
+      </c>
+      <c r="K93" t="n">
+        <v>25.71428571428571</v>
+      </c>
+      <c r="L93" t="n">
+        <v>10</v>
+      </c>
+      <c r="M93" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="N93" t="n">
+        <v>0.01133621164439703</v>
+      </c>
+      <c r="O93" t="n">
+        <v>-0.2759719832882769</v>
+      </c>
+      <c r="P93" t="n">
+        <v>0.1876869565217392</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101005C6577D0C3AE724BBB504F46D5A19401" ma:contentTypeVersion="18" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="17afb16e0fbe716d3dcf2481b32b5550">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="df76e320-99cb-4a11-b59f-8bf32867ab70" xmlns:ns3="c0789f30-979e-497b-8344-faefb3987540" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="f6d0bb8d4e6a5d6b988ea2ed2503dbb5" ns2:_="" ns3:_="">
+    <xsd:import namespace="df76e320-99cb-4a11-b59f-8bf32867ab70"/>
+    <xsd:import namespace="c0789f30-979e-497b-8344-faefb3987540"/>
+    <xsd:element name="properties">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element name="documentManagement">
+            <xsd:complexType>
+              <xsd:all>
+                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceAutoTags" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceAutoKeyPoints" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceKeyPoints" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
+                <xsd:element ref="ns3:SharedWithUsers" minOccurs="0"/>
+                <xsd:element ref="ns3:SharedWithDetails" minOccurs="0"/>
+                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
+                <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceLocation" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
+              </xsd:all>
+            </xsd:complexType>
+          </xsd:element>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="df76e320-99cb-4a11-b59f-8bf32867ab70" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceAutoTags" ma:index="10" nillable="true" ma:displayName="Tags" ma:internalName="MediaServiceAutoTags" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceOCR" ma:index="11" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceGenerationTime" ma:index="12" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceEventHashCode" ma:index="13" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceAutoKeyPoints" ma:index="14" nillable="true" ma:displayName="MediaServiceAutoKeyPoints" ma:hidden="true" ma:internalName="MediaServiceAutoKeyPoints" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceKeyPoints" ma:index="15" nillable="true" ma:displayName="KeyPoints" ma:internalName="MediaServiceKeyPoints" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceDateTaken" ma:index="16" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaLengthInSeconds" ma:index="17" nillable="true" ma:displayName="Length (seconds)" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Unknown"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="21" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="2ea5f6a7-5373-4784-9cd5-4ca8be386d98" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="MediaServiceLocation" ma:index="23" nillable="true" ma:displayName="Location" ma:description="" ma:indexed="true" ma:internalName="MediaServiceLocation" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="24" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:description="" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceSearchProperties" ma:index="25" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="c0789f30-979e-497b-8344-faefb3987540" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="SharedWithUsers" ma:index="18" nillable="true" ma:displayName="Shared With" ma:internalName="SharedWithUsers" ma:readOnly="true">
+      <xsd:complexType>
+        <xsd:complexContent>
+          <xsd:extension base="dms:UserMulti">
+            <xsd:sequence>
+              <xsd:element name="UserInfo" minOccurs="0" maxOccurs="unbounded">
+                <xsd:complexType>
+                  <xsd:sequence>
+                    <xsd:element name="DisplayName" type="xsd:string" minOccurs="0"/>
+                    <xsd:element name="AccountId" type="dms:UserId" minOccurs="0" nillable="true"/>
+                    <xsd:element name="AccountType" type="xsd:string" minOccurs="0"/>
+                  </xsd:sequence>
+                </xsd:complexType>
+              </xsd:element>
+            </xsd:sequence>
+          </xsd:extension>
+        </xsd:complexContent>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="SharedWithDetails" ma:index="19" nillable="true" ma:displayName="Shared With Details" ma:internalName="SharedWithDetails" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="TaxCatchAll" ma:index="22" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{f1100522-260f-4f17-9a31-47a12622b1e0}" ma:internalName="TaxCatchAll" ma:showField="CatchAllData" ma:web="c0789f30-979e-497b-8344-faefb3987540">
+      <xsd:complexType>
+        <xsd:complexContent>
+          <xsd:extension base="dms:MultiChoiceLookup">
+            <xsd:sequence>
+              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
+            </xsd:sequence>
+          </xsd:extension>
+        </xsd:complexContent>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
+    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
+    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
+    <xsd:element name="coreProperties" type="CT_coreProperties"/>
+    <xsd:complexType name="CT_coreProperties">
+      <xsd:all>
+        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
+        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
+        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
+          <xsd:annotation>
+            <xsd:documentation>
+                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
+                    </xsd:documentation>
+          </xsd:annotation>
+        </xsd:element>
+        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+      </xsd:all>
+    </xsd:complexType>
+  </xsd:schema>
+  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
+    <xs:element name="Person">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:DisplayName" minOccurs="0"/>
+          <xs:element ref="pc:AccountId" minOccurs="0"/>
+          <xs:element ref="pc:AccountType" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="DisplayName" type="xs:string"/>
+    <xs:element name="AccountId" type="xs:string"/>
+    <xs:element name="AccountType" type="xs:string"/>
+    <xs:element name="BDCAssociatedEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+        <xs:attribute ref="pc:EntityNamespace"/>
+        <xs:attribute ref="pc:EntityName"/>
+        <xs:attribute ref="pc:SystemInstanceName"/>
+        <xs:attribute ref="pc:AssociationName"/>
+      </xs:complexType>
+    </xs:element>
+    <xs:attribute name="EntityNamespace" type="xs:string"/>
+    <xs:attribute name="EntityName" type="xs:string"/>
+    <xs:attribute name="SystemInstanceName" type="xs:string"/>
+    <xs:attribute name="AssociationName" type="xs:string"/>
+    <xs:element name="BDCEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
+          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
+          <xs:element ref="pc:EntityId1" minOccurs="0"/>
+          <xs:element ref="pc:EntityId2" minOccurs="0"/>
+          <xs:element ref="pc:EntityId3" minOccurs="0"/>
+          <xs:element ref="pc:EntityId4" minOccurs="0"/>
+          <xs:element ref="pc:EntityId5" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="EntityDisplayName" type="xs:string"/>
+    <xs:element name="EntityInstanceReference" type="xs:string"/>
+    <xs:element name="EntityId1" type="xs:string"/>
+    <xs:element name="EntityId2" type="xs:string"/>
+    <xs:element name="EntityId3" type="xs:string"/>
+    <xs:element name="EntityId4" type="xs:string"/>
+    <xs:element name="EntityId5" type="xs:string"/>
+    <xs:element name="Terms">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermInfo">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermName" minOccurs="0"/>
+          <xs:element ref="pc:TermId" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermName" type="xs:string"/>
+    <xs:element name="TermId" type="xs:string"/>
+  </xs:schema>
+</ct:contentTypeSchema>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="c0789f30-979e-497b-8344-faefb3987540" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="df76e320-99cb-4a11-b59f-8bf32867ab70">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D76ACC3E-A92C-4679-B055-E234AD322405}"/>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A2AFBCA3-629C-490F-ACB7-AE9EAFFE36F9}"/>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E6B84EC6-443C-4DEF-A5B0-CD79C9EE9744}"/>
 </file>
--- a/AtchisonRegime/Outputs/USA/df_regSummary_USA.xlsx
+++ b/AtchisonRegime/Outputs/USA/df_regSummary_USA.xlsx
@@ -545,7 +545,7 @@
         <v>12.09637420237011</v>
       </c>
       <c r="K2" t="n">
-        <v>31.99426111908178</v>
+        <v>31.94842406876791</v>
       </c>
       <c r="L2" t="n">
         <v>23</v>
@@ -603,7 +603,7 @@
         <v>9.217830822195761</v>
       </c>
       <c r="K3" t="n">
-        <v>19.51219512195122</v>
+        <v>19.48424068767908</v>
       </c>
       <c r="L3" t="n">
         <v>21</v>
@@ -646,13 +646,13 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="G4" t="n">
-        <v>0.7664124010957496</v>
+        <v>0.843423352417042</v>
       </c>
       <c r="H4" t="n">
-        <v>3.526078736070417</v>
+        <v>3.609712577104466</v>
       </c>
       <c r="I4" t="n">
         <v>-10.75849917490121</v>
@@ -661,16 +661,16 @@
         <v>12.32175011776928</v>
       </c>
       <c r="K4" t="n">
-        <v>21.37733142037303</v>
+        <v>21.48997134670487</v>
       </c>
       <c r="L4" t="n">
         <v>22</v>
       </c>
       <c r="M4" t="n">
-        <v>6.772727272727272</v>
+        <v>6.818181818181818</v>
       </c>
       <c r="N4" t="n">
-        <v>0.05469268199246653</v>
+        <v>0.06048376590859612</v>
       </c>
       <c r="O4" t="n">
         <v>-0.1536265717473903</v>
@@ -719,7 +719,7 @@
         <v>11.60677491371982</v>
       </c>
       <c r="K5" t="n">
-        <v>27.11621233859398</v>
+        <v>27.07736389684814</v>
       </c>
       <c r="L5" t="n">
         <v>19</v>
@@ -777,7 +777,7 @@
         <v>8.955800344253511</v>
       </c>
       <c r="K6" t="n">
-        <v>38.2716049382716</v>
+        <v>38.03680981595092</v>
       </c>
       <c r="L6" t="n">
         <v>5</v>
@@ -835,7 +835,7 @@
         <v>10.3135151779801</v>
       </c>
       <c r="K7" t="n">
-        <v>19.75308641975309</v>
+        <v>19.6319018404908</v>
       </c>
       <c r="L7" t="n">
         <v>5</v>
@@ -878,13 +878,13 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G8" t="n">
-        <v>1.37189595591855</v>
+        <v>1.549624870638514</v>
       </c>
       <c r="H8" t="n">
-        <v>3.721847852811584</v>
+        <v>3.894596565763329</v>
       </c>
       <c r="I8" t="n">
         <v>-4.44559447216598</v>
@@ -893,16 +893,16 @@
         <v>9.418745103146341</v>
       </c>
       <c r="K8" t="n">
-        <v>20.98765432098765</v>
+        <v>21.47239263803681</v>
       </c>
       <c r="L8" t="n">
         <v>5</v>
       </c>
       <c r="M8" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="N8" t="n">
-        <v>0.1002622429611449</v>
+        <v>0.1162656527669002</v>
       </c>
       <c r="O8" t="n">
         <v>-0.04096620966264153</v>
@@ -951,7 +951,7 @@
         <v>11.1380905480897</v>
       </c>
       <c r="K9" t="n">
-        <v>20.98765432098765</v>
+        <v>20.85889570552147</v>
       </c>
       <c r="L9" t="n">
         <v>4</v>
@@ -1009,7 +1009,7 @@
         <v>13.9265910796816</v>
       </c>
       <c r="K10" t="n">
-        <v>38.2716049382716</v>
+        <v>38.03680981595092</v>
       </c>
       <c r="L10" t="n">
         <v>5</v>
@@ -1067,7 +1067,7 @@
         <v>9.04103299082419</v>
       </c>
       <c r="K11" t="n">
-        <v>19.75308641975309</v>
+        <v>19.6319018404908</v>
       </c>
       <c r="L11" t="n">
         <v>5</v>
@@ -1110,13 +1110,13 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G12" t="n">
-        <v>2.007931652282985</v>
+        <v>2.201817516950996</v>
       </c>
       <c r="H12" t="n">
-        <v>4.131130799882667</v>
+        <v>4.228475363413711</v>
       </c>
       <c r="I12" t="n">
         <v>-6.1677509153966</v>
@@ -1125,16 +1125,16 @@
         <v>9.668123981273439</v>
       </c>
       <c r="K12" t="n">
-        <v>20.98765432098765</v>
+        <v>21.47239263803681</v>
       </c>
       <c r="L12" t="n">
         <v>5</v>
       </c>
       <c r="M12" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="N12" t="n">
-        <v>0.148854616810747</v>
+        <v>0.1674296715749297</v>
       </c>
       <c r="O12" t="n">
         <v>0.01199096286142609</v>
@@ -1183,7 +1183,7 @@
         <v>17.1993335323565</v>
       </c>
       <c r="K13" t="n">
-        <v>20.98765432098765</v>
+        <v>20.85889570552147</v>
       </c>
       <c r="L13" t="n">
         <v>4</v>
@@ -1241,7 +1241,7 @@
         <v>9.823783930802669</v>
       </c>
       <c r="K14" t="n">
-        <v>38.2716049382716</v>
+        <v>38.03680981595092</v>
       </c>
       <c r="L14" t="n">
         <v>5</v>
@@ -1299,7 +1299,7 @@
         <v>7.74527627402691</v>
       </c>
       <c r="K15" t="n">
-        <v>19.75308641975309</v>
+        <v>19.6319018404908</v>
       </c>
       <c r="L15" t="n">
         <v>5</v>
@@ -1342,13 +1342,13 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G16" t="n">
-        <v>1.521601763880777</v>
+        <v>1.511800350376622</v>
       </c>
       <c r="H16" t="n">
-        <v>3.465956836136336</v>
+        <v>3.415098804184472</v>
       </c>
       <c r="I16" t="n">
         <v>-4.02566524721569</v>
@@ -1357,16 +1357,16 @@
         <v>10.3641980528429</v>
       </c>
       <c r="K16" t="n">
-        <v>20.98765432098765</v>
+        <v>21.47239263803681</v>
       </c>
       <c r="L16" t="n">
         <v>5</v>
       </c>
       <c r="M16" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="N16" t="n">
-        <v>0.1170543160003003</v>
+        <v>0.1194045229274187</v>
       </c>
       <c r="O16" t="n">
         <v>-0.04025665247215693</v>
@@ -1415,7 +1415,7 @@
         <v>9.57292159347422</v>
       </c>
       <c r="K17" t="n">
-        <v>20.98765432098765</v>
+        <v>20.85889570552147</v>
       </c>
       <c r="L17" t="n">
         <v>4</v>
@@ -1473,7 +1473,7 @@
         <v>21.6010537672175</v>
       </c>
       <c r="K18" t="n">
-        <v>38.2716049382716</v>
+        <v>38.03680981595092</v>
       </c>
       <c r="L18" t="n">
         <v>5</v>
@@ -1531,7 +1531,7 @@
         <v>11.4844653113646</v>
       </c>
       <c r="K19" t="n">
-        <v>19.75308641975309</v>
+        <v>19.6319018404908</v>
       </c>
       <c r="L19" t="n">
         <v>5</v>
@@ -1574,13 +1574,13 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.7351575918528768</v>
+        <v>-0.7082522668494455</v>
       </c>
       <c r="H20" t="n">
-        <v>5.50938236908935</v>
+        <v>5.430090839297009</v>
       </c>
       <c r="I20" t="n">
         <v>-15.9270162165717</v>
@@ -1589,19 +1589,19 @@
         <v>9.63714932872772</v>
       </c>
       <c r="K20" t="n">
-        <v>20.98765432098765</v>
+        <v>21.47239263803681</v>
       </c>
       <c r="L20" t="n">
         <v>5</v>
       </c>
       <c r="M20" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.05643978249866042</v>
+        <v>-0.05609179546559588</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.1575338130610734</v>
+        <v>-0.1557938778957507</v>
       </c>
       <c r="P20" t="n">
         <v>0.05045070008285246</v>
@@ -1647,7 +1647,7 @@
         <v>25.6080879391498</v>
       </c>
       <c r="K21" t="n">
-        <v>20.98765432098765</v>
+        <v>20.85889570552147</v>
       </c>
       <c r="L21" t="n">
         <v>4</v>
@@ -1705,7 +1705,7 @@
         <v>14.7955721617363</v>
       </c>
       <c r="K22" t="n">
-        <v>38.2716049382716</v>
+        <v>38.03680981595092</v>
       </c>
       <c r="L22" t="n">
         <v>5</v>
@@ -1763,7 +1763,7 @@
         <v>17.2630481734445</v>
       </c>
       <c r="K23" t="n">
-        <v>19.75308641975309</v>
+        <v>19.6319018404908</v>
       </c>
       <c r="L23" t="n">
         <v>5</v>
@@ -1806,13 +1806,13 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G24" t="n">
-        <v>1.285715974596975</v>
+        <v>1.357130886229785</v>
       </c>
       <c r="H24" t="n">
-        <v>4.336984778091733</v>
+        <v>4.293567440630953</v>
       </c>
       <c r="I24" t="n">
         <v>-6.284878505113629</v>
@@ -1821,16 +1821,16 @@
         <v>9.959724493416481</v>
       </c>
       <c r="K24" t="n">
-        <v>20.98765432098765</v>
+        <v>21.47239263803681</v>
       </c>
       <c r="L24" t="n">
         <v>5</v>
       </c>
       <c r="M24" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="N24" t="n">
-        <v>0.08950733909719655</v>
+        <v>0.09699720396222614</v>
       </c>
       <c r="O24" t="n">
         <v>-0.03954617158273233</v>
@@ -1879,7 +1879,7 @@
         <v>12.5443599847335</v>
       </c>
       <c r="K25" t="n">
-        <v>20.98765432098765</v>
+        <v>20.85889570552147</v>
       </c>
       <c r="L25" t="n">
         <v>4</v>
@@ -1937,7 +1937,7 @@
         <v>9.96890693734484</v>
       </c>
       <c r="K26" t="n">
-        <v>38.2716049382716</v>
+        <v>38.03680981595092</v>
       </c>
       <c r="L26" t="n">
         <v>5</v>
@@ -1995,7 +1995,7 @@
         <v>8.86970753112975</v>
       </c>
       <c r="K27" t="n">
-        <v>19.75308641975309</v>
+        <v>19.6319018404908</v>
       </c>
       <c r="L27" t="n">
         <v>5</v>
@@ -2038,13 +2038,13 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G28" t="n">
-        <v>0.8542954949666298</v>
+        <v>0.654397352395867</v>
       </c>
       <c r="H28" t="n">
-        <v>4.37064551921874</v>
+        <v>4.465341771432714</v>
       </c>
       <c r="I28" t="n">
         <v>-6.25513270553522</v>
@@ -2053,19 +2053,19 @@
         <v>7.651278631372289</v>
       </c>
       <c r="K28" t="n">
-        <v>20.98765432098765</v>
+        <v>21.47239263803681</v>
       </c>
       <c r="L28" t="n">
         <v>5</v>
       </c>
       <c r="M28" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="N28" t="n">
-        <v>0.06542015793403295</v>
+        <v>0.05461159837414566</v>
       </c>
       <c r="O28" t="n">
-        <v>-0.1201307322417331</v>
+        <v>-0.1741735300411695</v>
       </c>
       <c r="P28" t="n">
         <v>0.3681830232103689</v>
@@ -2111,7 +2111,7 @@
         <v>10.2757108623477</v>
       </c>
       <c r="K29" t="n">
-        <v>20.98765432098765</v>
+        <v>20.85889570552147</v>
       </c>
       <c r="L29" t="n">
         <v>4</v>
@@ -2169,7 +2169,7 @@
         <v>13.5073547998131</v>
       </c>
       <c r="K30" t="n">
-        <v>38.2716049382716</v>
+        <v>38.03680981595092</v>
       </c>
       <c r="L30" t="n">
         <v>5</v>
@@ -2227,7 +2227,7 @@
         <v>11.9900891508605</v>
       </c>
       <c r="K31" t="n">
-        <v>19.75308641975309</v>
+        <v>19.6319018404908</v>
       </c>
       <c r="L31" t="n">
         <v>5</v>
@@ -2270,13 +2270,13 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G32" t="n">
-        <v>1.296326368946536</v>
+        <v>1.492014303151072</v>
       </c>
       <c r="H32" t="n">
-        <v>3.516832116866826</v>
+        <v>3.653029170095819</v>
       </c>
       <c r="I32" t="n">
         <v>-6.39395114876894</v>
@@ -2285,16 +2285,16 @@
         <v>8.145404066105311</v>
       </c>
       <c r="K32" t="n">
-        <v>20.98765432098765</v>
+        <v>21.47239263803681</v>
       </c>
       <c r="L32" t="n">
         <v>5</v>
       </c>
       <c r="M32" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="N32" t="n">
-        <v>0.09261454287436935</v>
+        <v>0.10980368679848</v>
       </c>
       <c r="O32" t="n">
         <v>-0.01684894838002426</v>
@@ -2343,7 +2343,7 @@
         <v>14.5269451461826</v>
       </c>
       <c r="K33" t="n">
-        <v>20.98765432098765</v>
+        <v>20.85889570552147</v>
       </c>
       <c r="L33" t="n">
         <v>4</v>
@@ -2401,7 +2401,7 @@
         <v>13.0963168927553</v>
       </c>
       <c r="K34" t="n">
-        <v>38.2716049382716</v>
+        <v>38.03680981595092</v>
       </c>
       <c r="L34" t="n">
         <v>5</v>
@@ -2459,7 +2459,7 @@
         <v>10.24694135888</v>
       </c>
       <c r="K35" t="n">
-        <v>19.75308641975309</v>
+        <v>19.6319018404908</v>
       </c>
       <c r="L35" t="n">
         <v>5</v>
@@ -2502,13 +2502,13 @@
         </is>
       </c>
       <c r="F36" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G36" t="n">
-        <v>2.029911899528887</v>
+        <v>2.264027018619616</v>
       </c>
       <c r="H36" t="n">
-        <v>4.893011988614491</v>
+        <v>5.015550689600296</v>
       </c>
       <c r="I36" t="n">
         <v>-7.30568996040934</v>
@@ -2517,16 +2517,16 @@
         <v>11.138619523777</v>
       </c>
       <c r="K36" t="n">
-        <v>20.98765432098765</v>
+        <v>21.47239263803681</v>
       </c>
       <c r="L36" t="n">
         <v>5</v>
       </c>
       <c r="M36" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="N36" t="n">
-        <v>0.1455015765697016</v>
+        <v>0.1678056245084087</v>
       </c>
       <c r="O36" t="n">
         <v>0.005677846780164364</v>
@@ -2575,7 +2575,7 @@
         <v>11.8700581470654</v>
       </c>
       <c r="K37" t="n">
-        <v>20.98765432098765</v>
+        <v>20.85889570552147</v>
       </c>
       <c r="L37" t="n">
         <v>4</v>
@@ -2633,7 +2633,7 @@
         <v>10.2371026217823</v>
       </c>
       <c r="K38" t="n">
-        <v>38.2716049382716</v>
+        <v>38.03680981595092</v>
       </c>
       <c r="L38" t="n">
         <v>5</v>
@@ -2691,7 +2691,7 @@
         <v>9.97010822270626</v>
       </c>
       <c r="K39" t="n">
-        <v>19.75308641975309</v>
+        <v>19.6319018404908</v>
       </c>
       <c r="L39" t="n">
         <v>5</v>
@@ -2734,13 +2734,13 @@
         </is>
       </c>
       <c r="F40" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G40" t="n">
-        <v>0.8915243717915948</v>
+        <v>0.9336889360593791</v>
       </c>
       <c r="H40" t="n">
-        <v>4.730679242531885</v>
+        <v>4.667262087039326</v>
       </c>
       <c r="I40" t="n">
         <v>-8.02838978821635</v>
@@ -2749,19 +2749,19 @@
         <v>11.7139405168735</v>
       </c>
       <c r="K40" t="n">
-        <v>20.98765432098765</v>
+        <v>21.47239263803681</v>
       </c>
       <c r="L40" t="n">
         <v>5</v>
       </c>
       <c r="M40" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="N40" t="n">
-        <v>0.05701359303286968</v>
+        <v>0.06163029411436911</v>
       </c>
       <c r="O40" t="n">
-        <v>-0.02489501783391979</v>
+        <v>-0.01596672450639058</v>
       </c>
       <c r="P40" t="n">
         <v>0.1654960460136041</v>
@@ -2807,7 +2807,7 @@
         <v>9.589243507641781</v>
       </c>
       <c r="K41" t="n">
-        <v>20.98765432098765</v>
+        <v>20.85889570552147</v>
       </c>
       <c r="L41" t="n">
         <v>4</v>
@@ -2865,7 +2865,7 @@
         <v>9.6248306252491</v>
       </c>
       <c r="K42" t="n">
-        <v>33.65384615384615</v>
+        <v>33.33333333333333</v>
       </c>
       <c r="L42" t="n">
         <v>3</v>
@@ -2923,7 +2923,7 @@
         <v>6.84469377692436</v>
       </c>
       <c r="K43" t="n">
-        <v>25</v>
+        <v>24.76190476190476</v>
       </c>
       <c r="L43" t="n">
         <v>4</v>
@@ -2966,13 +2966,13 @@
         </is>
       </c>
       <c r="F44" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G44" t="n">
-        <v>1.079068656284822</v>
+        <v>1.01962883051534</v>
       </c>
       <c r="H44" t="n">
-        <v>3.306655305527381</v>
+        <v>3.159488758369196</v>
       </c>
       <c r="I44" t="n">
         <v>-3.81879077014958</v>
@@ -2981,19 +2981,19 @@
         <v>7.202297448723289</v>
       </c>
       <c r="K44" t="n">
-        <v>10.57692307692308</v>
+        <v>11.42857142857143</v>
       </c>
       <c r="L44" t="n">
         <v>3</v>
       </c>
       <c r="M44" t="n">
-        <v>3.666666666666667</v>
+        <v>4</v>
       </c>
       <c r="N44" t="n">
-        <v>0.04306198941126849</v>
+        <v>0.04423901906444897</v>
       </c>
       <c r="O44" t="n">
-        <v>-0.03466968806384974</v>
+        <v>-0.03113859910430827</v>
       </c>
       <c r="P44" t="n">
         <v>0.1869234320064637</v>
@@ -3039,7 +3039,7 @@
         <v>7.360199774148531</v>
       </c>
       <c r="K45" t="n">
-        <v>30.76923076923077</v>
+        <v>30.47619047619048</v>
       </c>
       <c r="L45" t="n">
         <v>3</v>
@@ -3097,7 +3097,7 @@
         <v>12.2158962489732</v>
       </c>
       <c r="K46" t="n">
-        <v>38.2716049382716</v>
+        <v>38.03680981595092</v>
       </c>
       <c r="L46" t="n">
         <v>5</v>
@@ -3155,7 +3155,7 @@
         <v>7.714682238485699</v>
       </c>
       <c r="K47" t="n">
-        <v>19.75308641975309</v>
+        <v>19.6319018404908</v>
       </c>
       <c r="L47" t="n">
         <v>5</v>
@@ -3198,13 +3198,13 @@
         </is>
       </c>
       <c r="F48" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G48" t="n">
-        <v>1.479291225980566</v>
+        <v>1.525477519988132</v>
       </c>
       <c r="H48" t="n">
-        <v>4.581673893450299</v>
+        <v>4.522056253204415</v>
       </c>
       <c r="I48" t="n">
         <v>-8.18149875021855</v>
@@ -3213,16 +3213,16 @@
         <v>10.9879016302789</v>
       </c>
       <c r="K48" t="n">
-        <v>20.98765432098765</v>
+        <v>21.47239263803681</v>
       </c>
       <c r="L48" t="n">
         <v>5</v>
       </c>
       <c r="M48" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="N48" t="n">
-        <v>0.1133377992206024</v>
+        <v>0.1195595176237868</v>
       </c>
       <c r="O48" t="n">
         <v>-0.08181498750218552</v>
@@ -3271,7 +3271,7 @@
         <v>6.83944264356443</v>
       </c>
       <c r="K49" t="n">
-        <v>20.98765432098765</v>
+        <v>20.85889570552147</v>
       </c>
       <c r="L49" t="n">
         <v>4</v>
@@ -3329,7 +3329,7 @@
         <v>6.95169290448147</v>
       </c>
       <c r="K50" t="n">
-        <v>32.06106870229007</v>
+        <v>31.81818181818182</v>
       </c>
       <c r="L50" t="n">
         <v>5</v>
@@ -3387,7 +3387,7 @@
         <v>7.285268265153571</v>
       </c>
       <c r="K51" t="n">
-        <v>19.84732824427481</v>
+        <v>19.6969696969697</v>
       </c>
       <c r="L51" t="n">
         <v>4</v>
@@ -3430,13 +3430,13 @@
         </is>
       </c>
       <c r="F52" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G52" t="n">
-        <v>1.189292861681597</v>
+        <v>1.329088159562841</v>
       </c>
       <c r="H52" t="n">
-        <v>3.803673103524818</v>
+        <v>3.824472368675238</v>
       </c>
       <c r="I52" t="n">
         <v>-6.986148218179911</v>
@@ -3445,16 +3445,16 @@
         <v>7.521483003263831</v>
       </c>
       <c r="K52" t="n">
-        <v>23.66412213740458</v>
+        <v>24.24242424242424</v>
       </c>
       <c r="L52" t="n">
         <v>4</v>
       </c>
       <c r="M52" t="n">
-        <v>7.75</v>
+        <v>8</v>
       </c>
       <c r="N52" t="n">
-        <v>0.0963880667567612</v>
+        <v>0.1109131716344917</v>
       </c>
       <c r="O52" t="n">
         <v>-0.03198909559765961</v>
@@ -3503,7 +3503,7 @@
         <v>8.975974874825891</v>
       </c>
       <c r="K53" t="n">
-        <v>24.42748091603053</v>
+        <v>24.24242424242424</v>
       </c>
       <c r="L53" t="n">
         <v>3</v>
@@ -3561,7 +3561,7 @@
         <v>7.6716417531022</v>
       </c>
       <c r="K54" t="n">
-        <v>32.06106870229007</v>
+        <v>31.81818181818182</v>
       </c>
       <c r="L54" t="n">
         <v>5</v>
@@ -3619,7 +3619,7 @@
         <v>6.94715275176028</v>
       </c>
       <c r="K55" t="n">
-        <v>19.84732824427481</v>
+        <v>19.6969696969697</v>
       </c>
       <c r="L55" t="n">
         <v>4</v>
@@ -3662,13 +3662,13 @@
         </is>
       </c>
       <c r="F56" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G56" t="n">
-        <v>1.319659665550913</v>
+        <v>1.470766084962072</v>
       </c>
       <c r="H56" t="n">
-        <v>3.505195498158436</v>
+        <v>3.552565402892394</v>
       </c>
       <c r="I56" t="n">
         <v>-5.24453965145917</v>
@@ -3677,16 +3677,16 @@
         <v>7.13073476203116</v>
       </c>
       <c r="K56" t="n">
-        <v>23.66412213740458</v>
+        <v>24.24242424242424</v>
       </c>
       <c r="L56" t="n">
         <v>4</v>
       </c>
       <c r="M56" t="n">
-        <v>7.75</v>
+        <v>8</v>
       </c>
       <c r="N56" t="n">
-        <v>0.1090877339913797</v>
+        <v>0.1248137021528484</v>
       </c>
       <c r="O56" t="n">
         <v>-0.01628597000901144</v>
@@ -3735,7 +3735,7 @@
         <v>7.925364439758551</v>
       </c>
       <c r="K57" t="n">
-        <v>24.42748091603053</v>
+        <v>24.24242424242424</v>
       </c>
       <c r="L57" t="n">
         <v>3</v>
@@ -3793,7 +3793,7 @@
         <v>7.36666934510836</v>
       </c>
       <c r="K58" t="n">
-        <v>32.06106870229007</v>
+        <v>31.81818181818182</v>
       </c>
       <c r="L58" t="n">
         <v>5</v>
@@ -3851,7 +3851,7 @@
         <v>7.93887645673724</v>
       </c>
       <c r="K59" t="n">
-        <v>19.84732824427481</v>
+        <v>19.6969696969697</v>
       </c>
       <c r="L59" t="n">
         <v>4</v>
@@ -3894,13 +3894,13 @@
         </is>
       </c>
       <c r="F60" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G60" t="n">
-        <v>1.667960216688404</v>
+        <v>1.683968509279623</v>
       </c>
       <c r="H60" t="n">
-        <v>3.4523374434225</v>
+        <v>3.397405224322854</v>
       </c>
       <c r="I60" t="n">
         <v>-4.57958033380678</v>
@@ -3909,16 +3909,16 @@
         <v>8.375876401854281</v>
       </c>
       <c r="K60" t="n">
-        <v>23.66412213740458</v>
+        <v>24.24242424242424</v>
       </c>
       <c r="L60" t="n">
         <v>4</v>
       </c>
       <c r="M60" t="n">
-        <v>7.75</v>
+        <v>8</v>
       </c>
       <c r="N60" t="n">
-        <v>0.1476393151596483</v>
+        <v>0.1530020732051695</v>
       </c>
       <c r="O60" t="n">
         <v>-0.04579580333806776</v>
@@ -3967,7 +3967,7 @@
         <v>6.87229435690348</v>
       </c>
       <c r="K61" t="n">
-        <v>24.42748091603053</v>
+        <v>24.24242424242424</v>
       </c>
       <c r="L61" t="n">
         <v>3</v>
@@ -4025,7 +4025,7 @@
         <v>6.89263768827785</v>
       </c>
       <c r="K62" t="n">
-        <v>32.06106870229007</v>
+        <v>31.81818181818182</v>
       </c>
       <c r="L62" t="n">
         <v>5</v>
@@ -4083,7 +4083,7 @@
         <v>7.2021582714579</v>
       </c>
       <c r="K63" t="n">
-        <v>19.84732824427481</v>
+        <v>19.6969696969697</v>
       </c>
       <c r="L63" t="n">
         <v>4</v>
@@ -4126,13 +4126,13 @@
         </is>
       </c>
       <c r="F64" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G64" t="n">
-        <v>1.367730661845499</v>
+        <v>1.513476847310727</v>
       </c>
       <c r="H64" t="n">
-        <v>3.509497511236934</v>
+        <v>3.549507909621306</v>
       </c>
       <c r="I64" t="n">
         <v>-5.23417007004207</v>
@@ -4141,16 +4141,16 @@
         <v>7.17869308850433</v>
       </c>
       <c r="K64" t="n">
-        <v>23.66412213740458</v>
+        <v>24.24242424242424</v>
       </c>
       <c r="L64" t="n">
         <v>4</v>
       </c>
       <c r="M64" t="n">
-        <v>7.75</v>
+        <v>8</v>
       </c>
       <c r="N64" t="n">
-        <v>0.1131540105365176</v>
+        <v>0.1286082319768208</v>
       </c>
       <c r="O64" t="n">
         <v>-0.01636330309291345</v>
@@ -4199,7 +4199,7 @@
         <v>8.24611022911178</v>
       </c>
       <c r="K65" t="n">
-        <v>24.42748091603053</v>
+        <v>24.24242424242424</v>
       </c>
       <c r="L65" t="n">
         <v>3</v>
@@ -4257,7 +4257,7 @@
         <v>11.7483945325047</v>
       </c>
       <c r="K66" t="n">
-        <v>38.19444444444444</v>
+        <v>37.93103448275862</v>
       </c>
       <c r="L66" t="n">
         <v>5</v>
@@ -4315,7 +4315,7 @@
         <v>7.42189952260202</v>
       </c>
       <c r="K67" t="n">
-        <v>18.05555555555555</v>
+        <v>17.93103448275862</v>
       </c>
       <c r="L67" t="n">
         <v>4</v>
@@ -4358,13 +4358,13 @@
         </is>
       </c>
       <c r="F68" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G68" t="n">
-        <v>1.82486140770451</v>
+        <v>2.010208026014461</v>
       </c>
       <c r="H68" t="n">
-        <v>3.513377893690257</v>
+        <v>3.611778530182588</v>
       </c>
       <c r="I68" t="n">
         <v>-3.99764824263489</v>
@@ -4373,16 +4373,16 @@
         <v>8.541253775102129</v>
       </c>
       <c r="K68" t="n">
-        <v>21.52777777777778</v>
+        <v>22.06896551724138</v>
       </c>
       <c r="L68" t="n">
         <v>4</v>
       </c>
       <c r="M68" t="n">
-        <v>7.75</v>
+        <v>8</v>
       </c>
       <c r="N68" t="n">
-        <v>0.1544951259325026</v>
+        <v>0.1753640032055443</v>
       </c>
       <c r="O68" t="n">
         <v>0.005915057912824206</v>
@@ -4431,7 +4431,7 @@
         <v>13.1224591254952</v>
       </c>
       <c r="K69" t="n">
-        <v>22.22222222222222</v>
+        <v>22.06896551724138</v>
       </c>
       <c r="L69" t="n">
         <v>3</v>
@@ -4489,7 +4489,7 @@
         <v>8.538804320682219</v>
       </c>
       <c r="K70" t="n">
-        <v>38.19444444444444</v>
+        <v>37.93103448275862</v>
       </c>
       <c r="L70" t="n">
         <v>5</v>
@@ -4547,7 +4547,7 @@
         <v>8.076570009882129</v>
       </c>
       <c r="K71" t="n">
-        <v>18.05555555555555</v>
+        <v>17.93103448275862</v>
       </c>
       <c r="L71" t="n">
         <v>4</v>
@@ -4590,13 +4590,13 @@
         </is>
       </c>
       <c r="F72" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G72" t="n">
-        <v>1.521348415428735</v>
+        <v>1.594824144500226</v>
       </c>
       <c r="H72" t="n">
-        <v>3.570036812116642</v>
+        <v>3.536493518036435</v>
       </c>
       <c r="I72" t="n">
         <v>-5.34515385225228</v>
@@ -4605,16 +4605,16 @@
         <v>7.72617150656165</v>
       </c>
       <c r="K72" t="n">
-        <v>21.52777777777778</v>
+        <v>22.06896551724138</v>
       </c>
       <c r="L72" t="n">
         <v>4</v>
       </c>
       <c r="M72" t="n">
-        <v>7.75</v>
+        <v>8</v>
       </c>
       <c r="N72" t="n">
-        <v>0.1289548522576497</v>
+        <v>0.1387257937951342</v>
       </c>
       <c r="O72" t="n">
         <v>-0.02496366494041635</v>
@@ -4663,7 +4663,7 @@
         <v>7.69497967124499</v>
       </c>
       <c r="K73" t="n">
-        <v>22.22222222222222</v>
+        <v>22.06896551724138</v>
       </c>
       <c r="L73" t="n">
         <v>3</v>
@@ -4721,7 +4721,7 @@
         <v>7.79885715856029</v>
       </c>
       <c r="K74" t="n">
-        <v>31.2</v>
+        <v>30.95238095238095</v>
       </c>
       <c r="L74" t="n">
         <v>4</v>
@@ -4779,7 +4779,7 @@
         <v>7.56280518804586</v>
       </c>
       <c r="K75" t="n">
-        <v>20.8</v>
+        <v>20.63492063492063</v>
       </c>
       <c r="L75" t="n">
         <v>4</v>
@@ -4822,13 +4822,13 @@
         </is>
       </c>
       <c r="F76" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="G76" t="n">
-        <v>0.8952174699847264</v>
+        <v>1.014776591478921</v>
       </c>
       <c r="H76" t="n">
-        <v>3.505631342934171</v>
+        <v>3.502153518436632</v>
       </c>
       <c r="I76" t="n">
         <v>-4.962450921223549</v>
@@ -4837,16 +4837,16 @@
         <v>6.989405251611849</v>
       </c>
       <c r="K76" t="n">
-        <v>22.4</v>
+        <v>23.01587301587302</v>
       </c>
       <c r="L76" t="n">
         <v>4</v>
       </c>
       <c r="M76" t="n">
-        <v>7</v>
+        <v>7.25</v>
       </c>
       <c r="N76" t="n">
-        <v>0.06264990668686923</v>
+        <v>0.07359321728799298</v>
       </c>
       <c r="O76" t="n">
         <v>-0.02210359171009768</v>
@@ -4895,7 +4895,7 @@
         <v>9.52544316828399</v>
       </c>
       <c r="K77" t="n">
-        <v>25.6</v>
+        <v>25.3968253968254</v>
       </c>
       <c r="L77" t="n">
         <v>3</v>
@@ -4953,7 +4953,7 @@
         <v>8.424126327671139</v>
       </c>
       <c r="K78" t="n">
-        <v>33.97260273972603</v>
+        <v>33.87978142076503</v>
       </c>
       <c r="L78" t="n">
         <v>13</v>
@@ -5011,7 +5011,7 @@
         <v>8.82228163422023</v>
       </c>
       <c r="K79" t="n">
-        <v>18.63013698630137</v>
+        <v>18.5792349726776</v>
       </c>
       <c r="L79" t="n">
         <v>12</v>
@@ -5054,13 +5054,13 @@
         </is>
       </c>
       <c r="F80" t="n">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G80" t="n">
-        <v>-0.2578925309576527</v>
+        <v>-0.2693054648146964</v>
       </c>
       <c r="H80" t="n">
-        <v>3.572345026311512</v>
+        <v>3.550503229191904</v>
       </c>
       <c r="I80" t="n">
         <v>-8.681400900200641</v>
@@ -5069,16 +5069,16 @@
         <v>9.379507611538331</v>
       </c>
       <c r="K80" t="n">
-        <v>21.0958904109589</v>
+        <v>21.31147540983606</v>
       </c>
       <c r="L80" t="n">
         <v>14</v>
       </c>
       <c r="M80" t="n">
-        <v>5.5</v>
+        <v>5.571428571428571</v>
       </c>
       <c r="N80" t="n">
-        <v>-0.01357023766335624</v>
+        <v>-0.01432177138170225</v>
       </c>
       <c r="O80" t="n">
         <v>-0.2172697385455662</v>
@@ -5127,7 +5127,7 @@
         <v>12.2526415215383</v>
       </c>
       <c r="K81" t="n">
-        <v>26.3013698630137</v>
+        <v>26.22950819672131</v>
       </c>
       <c r="L81" t="n">
         <v>12</v>
@@ -5185,7 +5185,7 @@
         <v>3.20100406514402</v>
       </c>
       <c r="K82" t="n">
-        <v>33.97260273972603</v>
+        <v>33.87978142076503</v>
       </c>
       <c r="L82" t="n">
         <v>13</v>
@@ -5243,7 +5243,7 @@
         <v>2.10200029059912</v>
       </c>
       <c r="K83" t="n">
-        <v>18.63013698630137</v>
+        <v>18.5792349726776</v>
       </c>
       <c r="L83" t="n">
         <v>12</v>
@@ -5286,13 +5286,13 @@
         </is>
       </c>
       <c r="F84" t="n">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G84" t="n">
-        <v>0.8090197869101518</v>
+        <v>0.7940425178640019</v>
       </c>
       <c r="H84" t="n">
-        <v>0.8336950578304456</v>
+        <v>0.8387596253209855</v>
       </c>
       <c r="I84" t="n">
         <v>-1.06770592199458</v>
@@ -5301,16 +5301,16 @@
         <v>3.69680550852241</v>
       </c>
       <c r="K84" t="n">
-        <v>21.0958904109589</v>
+        <v>21.31147540983606</v>
       </c>
       <c r="L84" t="n">
         <v>14</v>
       </c>
       <c r="M84" t="n">
-        <v>5.5</v>
+        <v>5.571428571428571</v>
       </c>
       <c r="N84" t="n">
-        <v>0.04593349216771875</v>
+        <v>0.04567542090651382</v>
       </c>
       <c r="O84" t="n">
         <v>-0.00650462170489563</v>
@@ -5359,7 +5359,7 @@
         <v>3.04477020602219</v>
       </c>
       <c r="K85" t="n">
-        <v>26.3013698630137</v>
+        <v>26.22950819672131</v>
       </c>
       <c r="L85" t="n">
         <v>12</v>
@@ -5417,7 +5417,7 @@
         <v>4.07926854837464</v>
       </c>
       <c r="K86" t="n">
-        <v>34.7972972972973</v>
+        <v>34.68013468013468</v>
       </c>
       <c r="L86" t="n">
         <v>10</v>
@@ -5475,7 +5475,7 @@
         <v>2.65425684189646</v>
       </c>
       <c r="K87" t="n">
-        <v>17.22972972972973</v>
+        <v>17.17171717171717</v>
       </c>
       <c r="L87" t="n">
         <v>10</v>
@@ -5518,13 +5518,13 @@
         </is>
       </c>
       <c r="F88" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="G88" t="n">
-        <v>0.7738529166745778</v>
+        <v>0.7623341816405129</v>
       </c>
       <c r="H88" t="n">
-        <v>0.94316923006219</v>
+        <v>0.9389660536149756</v>
       </c>
       <c r="I88" t="n">
         <v>-1.48836194752197</v>
@@ -5533,16 +5533,16 @@
         <v>2.70357383659126</v>
       </c>
       <c r="K88" t="n">
-        <v>19.25675675675676</v>
+        <v>19.52861952861953</v>
       </c>
       <c r="L88" t="n">
         <v>11</v>
       </c>
       <c r="M88" t="n">
-        <v>5.181818181818182</v>
+        <v>5.272727272727272</v>
       </c>
       <c r="N88" t="n">
-        <v>0.04116544808963199</v>
+        <v>0.04126220590326575</v>
       </c>
       <c r="O88" t="n">
         <v>-0.003616191384241962</v>
@@ -5591,7 +5591,7 @@
         <v>3.89681829021909</v>
       </c>
       <c r="K89" t="n">
-        <v>28.71621621621622</v>
+        <v>28.61952861952862</v>
       </c>
       <c r="L89" t="n">
         <v>11</v>
@@ -5649,7 +5649,7 @@
         <v>6.0219237887344</v>
       </c>
       <c r="K90" t="n">
-        <v>36.07142857142857</v>
+        <v>35.94306049822064</v>
       </c>
       <c r="L90" t="n">
         <v>10</v>
@@ -5707,7 +5707,7 @@
         <v>3.85016947536215</v>
       </c>
       <c r="K91" t="n">
-        <v>18.21428571428571</v>
+        <v>18.14946619217082</v>
       </c>
       <c r="L91" t="n">
         <v>10</v>
@@ -5750,13 +5750,13 @@
         </is>
       </c>
       <c r="F92" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G92" t="n">
-        <v>1.301039889505502</v>
+        <v>1.30707807573535</v>
       </c>
       <c r="H92" t="n">
-        <v>2.601939850776264</v>
+        <v>2.579006535013784</v>
       </c>
       <c r="I92" t="n">
         <v>-4.80976310122039</v>
@@ -5765,19 +5765,19 @@
         <v>10.5353534010951</v>
       </c>
       <c r="K92" t="n">
-        <v>20</v>
+        <v>20.2846975088968</v>
       </c>
       <c r="L92" t="n">
         <v>10</v>
       </c>
       <c r="M92" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="N92" t="n">
-        <v>0.0757621381929878</v>
+        <v>0.07743391747487838</v>
       </c>
       <c r="O92" t="n">
-        <v>0.01614546001046779</v>
+        <v>0.01986520042568296</v>
       </c>
       <c r="P92" t="n">
         <v>0.2690805038576816</v>
@@ -5823,7 +5823,7 @@
         <v>6.57176964259876</v>
       </c>
       <c r="K93" t="n">
-        <v>25.71428571428571</v>
+        <v>25.62277580071174</v>
       </c>
       <c r="L93" t="n">
         <v>10</v>
@@ -6122,13 +6122,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D76ACC3E-A92C-4679-B055-E234AD322405}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{099D5EDE-B862-4198-96B1-2C5A2765043F}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A2AFBCA3-629C-490F-ACB7-AE9EAFFE36F9}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7C11C7B4-BD83-4E8B-86F6-63A516D64913}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E6B84EC6-443C-4DEF-A5B0-CD79C9EE9744}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AA2664F9-5AB4-40E5-A790-F9D7EA900E67}"/>
 </file>
--- a/AtchisonRegime/Outputs/USA/df_regSummary_USA.xlsx
+++ b/AtchisonRegime/Outputs/USA/df_regSummary_USA.xlsx
@@ -530,13 +530,13 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="G2" t="n">
-        <v>1.516481591247468</v>
+        <v>1.613084980509627</v>
       </c>
       <c r="H2" t="n">
-        <v>2.697014155346433</v>
+        <v>2.806007472918573</v>
       </c>
       <c r="I2" t="n">
         <v>-5.920958484544303</v>
@@ -545,16 +545,16 @@
         <v>12.09637420237011</v>
       </c>
       <c r="K2" t="n">
-        <v>31.94842406876791</v>
+        <v>32.23965763195435</v>
       </c>
       <c r="L2" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="M2" t="n">
-        <v>9.695652173913043</v>
+        <v>9.416666666666666</v>
       </c>
       <c r="N2" t="n">
-        <v>0.1612964576781782</v>
+        <v>0.1665631956835631</v>
       </c>
       <c r="O2" t="n">
         <v>-0.09487463008282304</v>
@@ -603,7 +603,7 @@
         <v>9.217830822195761</v>
       </c>
       <c r="K3" t="n">
-        <v>19.48424068767908</v>
+        <v>19.40085592011413</v>
       </c>
       <c r="L3" t="n">
         <v>21</v>
@@ -661,7 +661,7 @@
         <v>12.32175011776928</v>
       </c>
       <c r="K4" t="n">
-        <v>21.48997134670487</v>
+        <v>21.39800285306705</v>
       </c>
       <c r="L4" t="n">
         <v>22</v>
@@ -719,7 +719,7 @@
         <v>11.60677491371982</v>
       </c>
       <c r="K5" t="n">
-        <v>27.07736389684814</v>
+        <v>26.96148359486448</v>
       </c>
       <c r="L5" t="n">
         <v>19</v>
@@ -762,13 +762,13 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="G6" t="n">
-        <v>1.817335207728831</v>
+        <v>2.139332209633503</v>
       </c>
       <c r="H6" t="n">
-        <v>4.128712880280975</v>
+        <v>4.292256932162904</v>
       </c>
       <c r="I6" t="n">
         <v>-8.49080820295638</v>
@@ -777,16 +777,16 @@
         <v>8.955800344253511</v>
       </c>
       <c r="K6" t="n">
-        <v>38.03680981595092</v>
+        <v>39.1566265060241</v>
       </c>
       <c r="L6" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M6" t="n">
-        <v>12.4</v>
+        <v>10.83333333333333</v>
       </c>
       <c r="N6" t="n">
-        <v>0.2569565713497336</v>
+        <v>0.2620801710926806</v>
       </c>
       <c r="O6" t="n">
         <v>-0.0260038557337664</v>
@@ -835,7 +835,7 @@
         <v>10.3135151779801</v>
       </c>
       <c r="K7" t="n">
-        <v>19.6319018404908</v>
+        <v>19.27710843373494</v>
       </c>
       <c r="L7" t="n">
         <v>5</v>
@@ -893,7 +893,7 @@
         <v>9.418745103146341</v>
       </c>
       <c r="K8" t="n">
-        <v>21.47239263803681</v>
+        <v>21.08433734939759</v>
       </c>
       <c r="L8" t="n">
         <v>5</v>
@@ -951,7 +951,7 @@
         <v>11.1380905480897</v>
       </c>
       <c r="K9" t="n">
-        <v>20.85889570552147</v>
+        <v>20.48192771084337</v>
       </c>
       <c r="L9" t="n">
         <v>4</v>
@@ -994,13 +994,13 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="G10" t="n">
-        <v>1.729678037418979</v>
+        <v>2.055720754876414</v>
       </c>
       <c r="H10" t="n">
-        <v>4.532677330944555</v>
+        <v>4.670479935499948</v>
       </c>
       <c r="I10" t="n">
         <v>-9.130168483852231</v>
@@ -1009,16 +1009,16 @@
         <v>13.9265910796816</v>
       </c>
       <c r="K10" t="n">
-        <v>38.03680981595092</v>
+        <v>39.1566265060241</v>
       </c>
       <c r="L10" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M10" t="n">
-        <v>12.4</v>
+        <v>10.83333333333333</v>
       </c>
       <c r="N10" t="n">
-        <v>0.250263525543147</v>
+        <v>0.2565026329205252</v>
       </c>
       <c r="O10" t="n">
         <v>-0.038663922363393</v>
@@ -1067,7 +1067,7 @@
         <v>9.04103299082419</v>
       </c>
       <c r="K11" t="n">
-        <v>19.6319018404908</v>
+        <v>19.27710843373494</v>
       </c>
       <c r="L11" t="n">
         <v>5</v>
@@ -1125,7 +1125,7 @@
         <v>9.668123981273439</v>
       </c>
       <c r="K12" t="n">
-        <v>21.47239263803681</v>
+        <v>21.08433734939759</v>
       </c>
       <c r="L12" t="n">
         <v>5</v>
@@ -1183,7 +1183,7 @@
         <v>17.1993335323565</v>
       </c>
       <c r="K13" t="n">
-        <v>20.85889570552147</v>
+        <v>20.48192771084337</v>
       </c>
       <c r="L13" t="n">
         <v>4</v>
@@ -1226,13 +1226,13 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="G14" t="n">
-        <v>1.255199854093324</v>
+        <v>1.251662274269111</v>
       </c>
       <c r="H14" t="n">
-        <v>3.297952272619971</v>
+        <v>3.219769624540545</v>
       </c>
       <c r="I14" t="n">
         <v>-4.66984504576325</v>
@@ -1241,16 +1241,16 @@
         <v>9.823783930802669</v>
       </c>
       <c r="K14" t="n">
-        <v>38.03680981595092</v>
+        <v>39.1566265060241</v>
       </c>
       <c r="L14" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M14" t="n">
-        <v>12.4</v>
+        <v>10.83333333333333</v>
       </c>
       <c r="N14" t="n">
-        <v>0.1784807312402021</v>
+        <v>0.154696426263512</v>
       </c>
       <c r="O14" t="n">
         <v>-0.03344483363254391</v>
@@ -1299,7 +1299,7 @@
         <v>7.74527627402691</v>
       </c>
       <c r="K15" t="n">
-        <v>19.6319018404908</v>
+        <v>19.27710843373494</v>
       </c>
       <c r="L15" t="n">
         <v>5</v>
@@ -1357,7 +1357,7 @@
         <v>10.3641980528429</v>
       </c>
       <c r="K16" t="n">
-        <v>21.47239263803681</v>
+        <v>21.08433734939759</v>
       </c>
       <c r="L16" t="n">
         <v>5</v>
@@ -1415,7 +1415,7 @@
         <v>9.57292159347422</v>
       </c>
       <c r="K17" t="n">
-        <v>20.85889570552147</v>
+        <v>20.48192771084337</v>
       </c>
       <c r="L17" t="n">
         <v>4</v>
@@ -1458,13 +1458,13 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="G18" t="n">
-        <v>1.274342131833923</v>
+        <v>1.225058438823152</v>
       </c>
       <c r="H18" t="n">
-        <v>6.003194643687698</v>
+        <v>5.865153850838523</v>
       </c>
       <c r="I18" t="n">
         <v>-11.8320411519501</v>
@@ -1473,16 +1473,16 @@
         <v>21.6010537672175</v>
       </c>
       <c r="K18" t="n">
-        <v>38.03680981595092</v>
+        <v>39.1566265060241</v>
       </c>
       <c r="L18" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M18" t="n">
-        <v>12.4</v>
+        <v>10.83333333333333</v>
       </c>
       <c r="N18" t="n">
-        <v>0.1662917430822683</v>
+        <v>0.1396112306600268</v>
       </c>
       <c r="O18" t="n">
         <v>-0.1283343741738839</v>
@@ -1531,7 +1531,7 @@
         <v>11.4844653113646</v>
       </c>
       <c r="K19" t="n">
-        <v>19.6319018404908</v>
+        <v>19.27710843373494</v>
       </c>
       <c r="L19" t="n">
         <v>5</v>
@@ -1589,7 +1589,7 @@
         <v>9.63714932872772</v>
       </c>
       <c r="K20" t="n">
-        <v>21.47239263803681</v>
+        <v>21.08433734939759</v>
       </c>
       <c r="L20" t="n">
         <v>5</v>
@@ -1647,7 +1647,7 @@
         <v>25.6080879391498</v>
       </c>
       <c r="K21" t="n">
-        <v>20.85889570552147</v>
+        <v>20.48192771084337</v>
       </c>
       <c r="L21" t="n">
         <v>4</v>
@@ -1690,13 +1690,13 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="G22" t="n">
-        <v>2.29098455622489</v>
+        <v>2.359950094325834</v>
       </c>
       <c r="H22" t="n">
-        <v>4.517860264604721</v>
+        <v>4.422004576986046</v>
       </c>
       <c r="I22" t="n">
         <v>-7.834552959385981</v>
@@ -1705,16 +1705,16 @@
         <v>14.7955721617363</v>
       </c>
       <c r="K22" t="n">
-        <v>38.03680981595092</v>
+        <v>39.1566265060241</v>
       </c>
       <c r="L22" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M22" t="n">
-        <v>12.4</v>
+        <v>10.83333333333333</v>
       </c>
       <c r="N22" t="n">
-        <v>0.3497317708204247</v>
+        <v>0.3110947722145022</v>
       </c>
       <c r="O22" t="n">
         <v>-0.04384403286972716</v>
@@ -1763,7 +1763,7 @@
         <v>17.2630481734445</v>
       </c>
       <c r="K23" t="n">
-        <v>19.6319018404908</v>
+        <v>19.27710843373494</v>
       </c>
       <c r="L23" t="n">
         <v>5</v>
@@ -1821,7 +1821,7 @@
         <v>9.959724493416481</v>
       </c>
       <c r="K24" t="n">
-        <v>21.47239263803681</v>
+        <v>21.08433734939759</v>
       </c>
       <c r="L24" t="n">
         <v>5</v>
@@ -1879,7 +1879,7 @@
         <v>12.5443599847335</v>
       </c>
       <c r="K25" t="n">
-        <v>20.85889570552147</v>
+        <v>20.48192771084337</v>
       </c>
       <c r="L25" t="n">
         <v>4</v>
@@ -1922,34 +1922,34 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="G26" t="n">
-        <v>1.591603206236816</v>
+        <v>1.234661235410037</v>
       </c>
       <c r="H26" t="n">
-        <v>3.401809869290509</v>
+        <v>3.701903585524569</v>
       </c>
       <c r="I26" t="n">
-        <v>-4.70593736639751</v>
+        <v>-6.14213949501007</v>
       </c>
       <c r="J26" t="n">
         <v>9.96890693734484</v>
       </c>
       <c r="K26" t="n">
-        <v>38.03680981595092</v>
+        <v>39.1566265060241</v>
       </c>
       <c r="L26" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M26" t="n">
-        <v>12.4</v>
+        <v>10.83333333333333</v>
       </c>
       <c r="N26" t="n">
-        <v>0.2492382914820463</v>
+        <v>0.1788355530383557</v>
       </c>
       <c r="O26" t="n">
-        <v>-0.03629388667361888</v>
+        <v>-0.1731781391800977</v>
       </c>
       <c r="P26" t="n">
         <v>0.9411700814490742</v>
@@ -1995,7 +1995,7 @@
         <v>8.86970753112975</v>
       </c>
       <c r="K27" t="n">
-        <v>19.6319018404908</v>
+        <v>19.27710843373494</v>
       </c>
       <c r="L27" t="n">
         <v>5</v>
@@ -2053,7 +2053,7 @@
         <v>7.651278631372289</v>
       </c>
       <c r="K28" t="n">
-        <v>21.47239263803681</v>
+        <v>21.08433734939759</v>
       </c>
       <c r="L28" t="n">
         <v>5</v>
@@ -2111,7 +2111,7 @@
         <v>10.2757108623477</v>
       </c>
       <c r="K29" t="n">
-        <v>20.85889570552147</v>
+        <v>20.48192771084337</v>
       </c>
       <c r="L29" t="n">
         <v>4</v>
@@ -2154,13 +2154,13 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="G30" t="n">
-        <v>1.939399161532498</v>
+        <v>2.225830157128166</v>
       </c>
       <c r="H30" t="n">
-        <v>4.183119601461454</v>
+        <v>4.289555957031482</v>
       </c>
       <c r="I30" t="n">
         <v>-5.93862228897025</v>
@@ -2169,16 +2169,16 @@
         <v>13.5073547998131</v>
       </c>
       <c r="K30" t="n">
-        <v>38.03680981595092</v>
+        <v>39.1566265060241</v>
       </c>
       <c r="L30" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M30" t="n">
-        <v>12.4</v>
+        <v>10.83333333333333</v>
       </c>
       <c r="N30" t="n">
-        <v>0.2855275258317235</v>
+        <v>0.2820740769054846</v>
       </c>
       <c r="O30" t="n">
         <v>-0.006648237576164506</v>
@@ -2227,7 +2227,7 @@
         <v>11.9900891508605</v>
       </c>
       <c r="K31" t="n">
-        <v>19.6319018404908</v>
+        <v>19.27710843373494</v>
       </c>
       <c r="L31" t="n">
         <v>5</v>
@@ -2285,7 +2285,7 @@
         <v>8.145404066105311</v>
       </c>
       <c r="K32" t="n">
-        <v>21.47239263803681</v>
+        <v>21.08433734939759</v>
       </c>
       <c r="L32" t="n">
         <v>5</v>
@@ -2343,7 +2343,7 @@
         <v>14.5269451461826</v>
       </c>
       <c r="K33" t="n">
-        <v>20.85889570552147</v>
+        <v>20.48192771084337</v>
       </c>
       <c r="L33" t="n">
         <v>4</v>
@@ -2386,13 +2386,13 @@
         </is>
       </c>
       <c r="F34" t="n">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="G34" t="n">
-        <v>2.093851115554846</v>
+        <v>2.469086036423287</v>
       </c>
       <c r="H34" t="n">
-        <v>4.267889535836972</v>
+        <v>4.507373738884525</v>
       </c>
       <c r="I34" t="n">
         <v>-9.03342228644261</v>
@@ -2401,16 +2401,16 @@
         <v>13.0963168927553</v>
       </c>
       <c r="K34" t="n">
-        <v>38.03680981595092</v>
+        <v>39.1566265060241</v>
       </c>
       <c r="L34" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M34" t="n">
-        <v>12.4</v>
+        <v>10.83333333333333</v>
       </c>
       <c r="N34" t="n">
-        <v>0.3013602524333251</v>
+        <v>0.3076578139205743</v>
       </c>
       <c r="O34" t="n">
         <v>0.0376879500447278</v>
@@ -2459,7 +2459,7 @@
         <v>10.24694135888</v>
       </c>
       <c r="K35" t="n">
-        <v>19.6319018404908</v>
+        <v>19.27710843373494</v>
       </c>
       <c r="L35" t="n">
         <v>5</v>
@@ -2517,7 +2517,7 @@
         <v>11.138619523777</v>
       </c>
       <c r="K36" t="n">
-        <v>21.47239263803681</v>
+        <v>21.08433734939759</v>
       </c>
       <c r="L36" t="n">
         <v>5</v>
@@ -2575,7 +2575,7 @@
         <v>11.8700581470654</v>
       </c>
       <c r="K37" t="n">
-        <v>20.85889570552147</v>
+        <v>20.48192771084337</v>
       </c>
       <c r="L37" t="n">
         <v>4</v>
@@ -2618,13 +2618,13 @@
         </is>
       </c>
       <c r="F38" t="n">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="G38" t="n">
-        <v>1.473376362221011</v>
+        <v>1.514633643402996</v>
       </c>
       <c r="H38" t="n">
-        <v>3.612573251183403</v>
+        <v>3.531948797756537</v>
       </c>
       <c r="I38" t="n">
         <v>-6.119052067979229</v>
@@ -2633,16 +2633,16 @@
         <v>10.2371026217823</v>
       </c>
       <c r="K38" t="n">
-        <v>38.03680981595092</v>
+        <v>39.1566265060241</v>
       </c>
       <c r="L38" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M38" t="n">
-        <v>12.4</v>
+        <v>10.83333333333333</v>
       </c>
       <c r="N38" t="n">
-        <v>0.2161631940696445</v>
+        <v>0.1922548284262004</v>
       </c>
       <c r="O38" t="n">
         <v>-0.02919700639085454</v>
@@ -2691,7 +2691,7 @@
         <v>9.97010822270626</v>
       </c>
       <c r="K39" t="n">
-        <v>19.6319018404908</v>
+        <v>19.27710843373494</v>
       </c>
       <c r="L39" t="n">
         <v>5</v>
@@ -2749,7 +2749,7 @@
         <v>11.7139405168735</v>
       </c>
       <c r="K40" t="n">
-        <v>21.47239263803681</v>
+        <v>21.08433734939759</v>
       </c>
       <c r="L40" t="n">
         <v>5</v>
@@ -2807,7 +2807,7 @@
         <v>9.589243507641781</v>
       </c>
       <c r="K41" t="n">
-        <v>20.85889570552147</v>
+        <v>20.48192771084337</v>
       </c>
       <c r="L41" t="n">
         <v>4</v>
@@ -2850,13 +2850,13 @@
         </is>
       </c>
       <c r="F42" t="n">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="G42" t="n">
-        <v>1.033442711355242</v>
+        <v>0.9807333457522788</v>
       </c>
       <c r="H42" t="n">
-        <v>4.070343018551587</v>
+        <v>3.90610485708021</v>
       </c>
       <c r="I42" t="n">
         <v>-8.10424767618815</v>
@@ -2865,16 +2865,16 @@
         <v>9.6248306252491</v>
       </c>
       <c r="K42" t="n">
-        <v>33.33333333333333</v>
+        <v>35.18518518518518</v>
       </c>
       <c r="L42" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M42" t="n">
-        <v>11.66666666666667</v>
+        <v>9.5</v>
       </c>
       <c r="N42" t="n">
-        <v>0.1210484640780234</v>
+        <v>0.09353982611266054</v>
       </c>
       <c r="O42" t="n">
         <v>0.007551522381175291</v>
@@ -2923,7 +2923,7 @@
         <v>6.84469377692436</v>
       </c>
       <c r="K43" t="n">
-        <v>24.76190476190476</v>
+        <v>24.07407407407407</v>
       </c>
       <c r="L43" t="n">
         <v>4</v>
@@ -2981,7 +2981,7 @@
         <v>7.202297448723289</v>
       </c>
       <c r="K44" t="n">
-        <v>11.42857142857143</v>
+        <v>11.11111111111111</v>
       </c>
       <c r="L44" t="n">
         <v>3</v>
@@ -3039,7 +3039,7 @@
         <v>7.360199774148531</v>
       </c>
       <c r="K45" t="n">
-        <v>30.47619047619048</v>
+        <v>29.62962962962963</v>
       </c>
       <c r="L45" t="n">
         <v>3</v>
@@ -3082,13 +3082,13 @@
         </is>
       </c>
       <c r="F46" t="n">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="G46" t="n">
-        <v>1.253244686663834</v>
+        <v>1.33828623264452</v>
       </c>
       <c r="H46" t="n">
-        <v>4.441448997007622</v>
+        <v>4.353571978386257</v>
       </c>
       <c r="I46" t="n">
         <v>-7.088565609126809</v>
@@ -3097,16 +3097,16 @@
         <v>12.2158962489732</v>
       </c>
       <c r="K46" t="n">
-        <v>38.03680981595092</v>
+        <v>39.1566265060241</v>
       </c>
       <c r="L46" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M46" t="n">
-        <v>12.4</v>
+        <v>10.83333333333333</v>
       </c>
       <c r="N46" t="n">
-        <v>0.1674438087671844</v>
+        <v>0.155499712402602</v>
       </c>
       <c r="O46" t="n">
         <v>-0.0430587583608022</v>
@@ -3155,7 +3155,7 @@
         <v>7.714682238485699</v>
       </c>
       <c r="K47" t="n">
-        <v>19.6319018404908</v>
+        <v>19.27710843373494</v>
       </c>
       <c r="L47" t="n">
         <v>5</v>
@@ -3213,7 +3213,7 @@
         <v>10.9879016302789</v>
       </c>
       <c r="K48" t="n">
-        <v>21.47239263803681</v>
+        <v>21.08433734939759</v>
       </c>
       <c r="L48" t="n">
         <v>5</v>
@@ -3271,7 +3271,7 @@
         <v>6.83944264356443</v>
       </c>
       <c r="K49" t="n">
-        <v>20.85889570552147</v>
+        <v>20.48192771084337</v>
       </c>
       <c r="L49" t="n">
         <v>4</v>
@@ -3314,13 +3314,13 @@
         </is>
       </c>
       <c r="F50" t="n">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="G50" t="n">
-        <v>1.542439071048227</v>
+        <v>1.817125959237107</v>
       </c>
       <c r="H50" t="n">
-        <v>3.24235854617211</v>
+        <v>3.297946210561716</v>
       </c>
       <c r="I50" t="n">
         <v>-5.54358074682365</v>
@@ -3329,16 +3329,16 @@
         <v>6.95169290448147</v>
       </c>
       <c r="K50" t="n">
-        <v>31.81818181818182</v>
+        <v>33.33333333333333</v>
       </c>
       <c r="L50" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M50" t="n">
-        <v>8.4</v>
+        <v>7.5</v>
       </c>
       <c r="N50" t="n">
-        <v>0.1423933908336546</v>
+        <v>0.1486084677661628</v>
       </c>
       <c r="O50" t="n">
         <v>-0.02750881203672606</v>
@@ -3387,7 +3387,7 @@
         <v>7.285268265153571</v>
       </c>
       <c r="K51" t="n">
-        <v>19.6969696969697</v>
+        <v>19.25925925925926</v>
       </c>
       <c r="L51" t="n">
         <v>4</v>
@@ -3445,7 +3445,7 @@
         <v>7.521483003263831</v>
       </c>
       <c r="K52" t="n">
-        <v>24.24242424242424</v>
+        <v>23.70370370370371</v>
       </c>
       <c r="L52" t="n">
         <v>4</v>
@@ -3503,7 +3503,7 @@
         <v>8.975974874825891</v>
       </c>
       <c r="K53" t="n">
-        <v>24.24242424242424</v>
+        <v>23.70370370370371</v>
       </c>
       <c r="L53" t="n">
         <v>3</v>
@@ -3546,13 +3546,13 @@
         </is>
       </c>
       <c r="F54" t="n">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="G54" t="n">
-        <v>1.480901384204729</v>
+        <v>1.792512297704946</v>
       </c>
       <c r="H54" t="n">
-        <v>3.279096359932725</v>
+        <v>3.377819523061516</v>
       </c>
       <c r="I54" t="n">
         <v>-5.82279192050039</v>
@@ -3561,16 +3561,16 @@
         <v>7.6716417531022</v>
       </c>
       <c r="K54" t="n">
-        <v>31.81818181818182</v>
+        <v>33.33333333333333</v>
       </c>
       <c r="L54" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M54" t="n">
-        <v>8.4</v>
+        <v>7.5</v>
       </c>
       <c r="N54" t="n">
-        <v>0.1339981301961045</v>
+        <v>0.1443735391699064</v>
       </c>
       <c r="O54" t="n">
         <v>-0.02026323853882039</v>
@@ -3619,7 +3619,7 @@
         <v>6.94715275176028</v>
       </c>
       <c r="K55" t="n">
-        <v>19.6969696969697</v>
+        <v>19.25925925925926</v>
       </c>
       <c r="L55" t="n">
         <v>4</v>
@@ -3677,7 +3677,7 @@
         <v>7.13073476203116</v>
       </c>
       <c r="K56" t="n">
-        <v>24.24242424242424</v>
+        <v>23.70370370370371</v>
       </c>
       <c r="L56" t="n">
         <v>4</v>
@@ -3735,7 +3735,7 @@
         <v>7.925364439758551</v>
       </c>
       <c r="K57" t="n">
-        <v>24.24242424242424</v>
+        <v>23.70370370370371</v>
       </c>
       <c r="L57" t="n">
         <v>3</v>
@@ -3778,13 +3778,13 @@
         </is>
       </c>
       <c r="F58" t="n">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="G58" t="n">
-        <v>1.351951188266407</v>
+        <v>1.407169481022475</v>
       </c>
       <c r="H58" t="n">
-        <v>3.264579378436513</v>
+        <v>3.1582414804589</v>
       </c>
       <c r="I58" t="n">
         <v>-4.41020346327878</v>
@@ -3793,16 +3793,16 @@
         <v>7.36666934510836</v>
       </c>
       <c r="K58" t="n">
-        <v>31.81818181818182</v>
+        <v>33.33333333333333</v>
       </c>
       <c r="L58" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M58" t="n">
-        <v>8.4</v>
+        <v>7.5</v>
       </c>
       <c r="N58" t="n">
-        <v>0.1237357192886825</v>
+        <v>0.1142536237255823</v>
       </c>
       <c r="O58" t="n">
         <v>-0.01152848052935629</v>
@@ -3851,7 +3851,7 @@
         <v>7.93887645673724</v>
       </c>
       <c r="K59" t="n">
-        <v>19.6969696969697</v>
+        <v>19.25925925925926</v>
       </c>
       <c r="L59" t="n">
         <v>4</v>
@@ -3909,7 +3909,7 @@
         <v>8.375876401854281</v>
       </c>
       <c r="K60" t="n">
-        <v>24.24242424242424</v>
+        <v>23.70370370370371</v>
       </c>
       <c r="L60" t="n">
         <v>4</v>
@@ -3967,7 +3967,7 @@
         <v>6.87229435690348</v>
       </c>
       <c r="K61" t="n">
-        <v>24.24242424242424</v>
+        <v>23.70370370370371</v>
       </c>
       <c r="L61" t="n">
         <v>3</v>
@@ -4010,13 +4010,13 @@
         </is>
       </c>
       <c r="F62" t="n">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="G62" t="n">
-        <v>1.674763436267108</v>
+        <v>1.965219780298155</v>
       </c>
       <c r="H62" t="n">
-        <v>3.229643246726068</v>
+        <v>3.305657323068291</v>
       </c>
       <c r="I62" t="n">
         <v>-5.997547424664449</v>
@@ -4025,16 +4025,16 @@
         <v>6.89263768827785</v>
       </c>
       <c r="K62" t="n">
-        <v>31.81818181818182</v>
+        <v>33.33333333333333</v>
       </c>
       <c r="L62" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M62" t="n">
-        <v>8.4</v>
+        <v>7.5</v>
       </c>
       <c r="N62" t="n">
-        <v>0.1548793911144378</v>
+        <v>0.1610797893162194</v>
       </c>
       <c r="O62" t="n">
         <v>-0.01208145336572686</v>
@@ -4083,7 +4083,7 @@
         <v>7.2021582714579</v>
       </c>
       <c r="K63" t="n">
-        <v>19.6969696969697</v>
+        <v>19.25925925925926</v>
       </c>
       <c r="L63" t="n">
         <v>4</v>
@@ -4141,7 +4141,7 @@
         <v>7.17869308850433</v>
       </c>
       <c r="K64" t="n">
-        <v>24.24242424242424</v>
+        <v>23.70370370370371</v>
       </c>
       <c r="L64" t="n">
         <v>4</v>
@@ -4199,7 +4199,7 @@
         <v>8.24611022911178</v>
       </c>
       <c r="K65" t="n">
-        <v>24.24242424242424</v>
+        <v>23.70370370370371</v>
       </c>
       <c r="L65" t="n">
         <v>3</v>
@@ -4242,13 +4242,13 @@
         </is>
       </c>
       <c r="F66" t="n">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="G66" t="n">
-        <v>1.852079742450122</v>
+        <v>2.157452507165958</v>
       </c>
       <c r="H66" t="n">
-        <v>3.93481658177471</v>
+        <v>4.050619882053869</v>
       </c>
       <c r="I66" t="n">
         <v>-6.747234236335339</v>
@@ -4257,16 +4257,16 @@
         <v>11.7483945325047</v>
       </c>
       <c r="K66" t="n">
-        <v>37.93103448275862</v>
+        <v>39.18918918918919</v>
       </c>
       <c r="L66" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M66" t="n">
-        <v>11</v>
+        <v>9.666666666666666</v>
       </c>
       <c r="N66" t="n">
-        <v>0.2290583342417606</v>
+        <v>0.2327472113150452</v>
       </c>
       <c r="O66" t="n">
         <v>-0.01023538750965192</v>
@@ -4315,7 +4315,7 @@
         <v>7.42189952260202</v>
       </c>
       <c r="K67" t="n">
-        <v>17.93103448275862</v>
+        <v>17.56756756756757</v>
       </c>
       <c r="L67" t="n">
         <v>4</v>
@@ -4373,7 +4373,7 @@
         <v>8.541253775102129</v>
       </c>
       <c r="K68" t="n">
-        <v>22.06896551724138</v>
+        <v>21.62162162162162</v>
       </c>
       <c r="L68" t="n">
         <v>4</v>
@@ -4431,7 +4431,7 @@
         <v>13.1224591254952</v>
       </c>
       <c r="K69" t="n">
-        <v>22.06896551724138</v>
+        <v>21.62162162162162</v>
       </c>
       <c r="L69" t="n">
         <v>3</v>
@@ -4474,13 +4474,13 @@
         </is>
       </c>
       <c r="F70" t="n">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="G70" t="n">
-        <v>1.611249289018029</v>
+        <v>1.728214243674844</v>
       </c>
       <c r="H70" t="n">
-        <v>3.343978758250776</v>
+        <v>3.293762642967363</v>
       </c>
       <c r="I70" t="n">
         <v>-6.02684421181042</v>
@@ -4489,16 +4489,16 @@
         <v>8.538804320682219</v>
       </c>
       <c r="K70" t="n">
-        <v>37.93103448275862</v>
+        <v>39.18918918918919</v>
       </c>
       <c r="L70" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M70" t="n">
-        <v>11</v>
+        <v>9.666666666666666</v>
       </c>
       <c r="N70" t="n">
-        <v>0.1956956467076387</v>
+        <v>0.1832020842862572</v>
       </c>
       <c r="O70" t="n">
         <v>-0.01060235851672997</v>
@@ -4547,7 +4547,7 @@
         <v>8.076570009882129</v>
       </c>
       <c r="K71" t="n">
-        <v>17.93103448275862</v>
+        <v>17.56756756756757</v>
       </c>
       <c r="L71" t="n">
         <v>4</v>
@@ -4605,7 +4605,7 @@
         <v>7.72617150656165</v>
       </c>
       <c r="K72" t="n">
-        <v>22.06896551724138</v>
+        <v>21.62162162162162</v>
       </c>
       <c r="L72" t="n">
         <v>4</v>
@@ -4663,7 +4663,7 @@
         <v>7.69497967124499</v>
       </c>
       <c r="K73" t="n">
-        <v>22.06896551724138</v>
+        <v>21.62162162162162</v>
       </c>
       <c r="L73" t="n">
         <v>3</v>
@@ -4706,13 +4706,13 @@
         </is>
       </c>
       <c r="F74" t="n">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="G74" t="n">
-        <v>1.427856165170456</v>
+        <v>1.637468724323736</v>
       </c>
       <c r="H74" t="n">
-        <v>3.338090341682212</v>
+        <v>3.303427728063657</v>
       </c>
       <c r="I74" t="n">
         <v>-4.88900426378396</v>
@@ -4721,16 +4721,16 @@
         <v>7.79885715856029</v>
       </c>
       <c r="K74" t="n">
-        <v>30.95238095238095</v>
+        <v>32.55813953488372</v>
       </c>
       <c r="L74" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M74" t="n">
-        <v>9.75</v>
+        <v>8.4</v>
       </c>
       <c r="N74" t="n">
-        <v>0.1514102785121009</v>
+        <v>0.1484612676687652</v>
       </c>
       <c r="O74" t="n">
         <v>-0.0119688944570685</v>
@@ -4779,7 +4779,7 @@
         <v>7.56280518804586</v>
       </c>
       <c r="K75" t="n">
-        <v>20.63492063492063</v>
+        <v>20.15503875968992</v>
       </c>
       <c r="L75" t="n">
         <v>4</v>
@@ -4837,7 +4837,7 @@
         <v>6.989405251611849</v>
       </c>
       <c r="K76" t="n">
-        <v>23.01587301587302</v>
+        <v>22.48062015503876</v>
       </c>
       <c r="L76" t="n">
         <v>4</v>
@@ -4895,7 +4895,7 @@
         <v>9.52544316828399</v>
       </c>
       <c r="K77" t="n">
-        <v>25.3968253968254</v>
+        <v>24.8062015503876</v>
       </c>
       <c r="L77" t="n">
         <v>3</v>
@@ -4938,13 +4938,13 @@
         </is>
       </c>
       <c r="F78" t="n">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="G78" t="n">
-        <v>0.6797013860230806</v>
+        <v>0.6365249429247308</v>
       </c>
       <c r="H78" t="n">
-        <v>3.224069697337324</v>
+        <v>3.197624069020038</v>
       </c>
       <c r="I78" t="n">
         <v>-7.181241138839139</v>
@@ -4953,16 +4953,16 @@
         <v>8.424126327671139</v>
       </c>
       <c r="K78" t="n">
-        <v>33.87978142076503</v>
+        <v>34.41734417344173</v>
       </c>
       <c r="L78" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="M78" t="n">
-        <v>9.538461538461538</v>
+        <v>9.071428571428571</v>
       </c>
       <c r="N78" t="n">
-        <v>0.06673588292886144</v>
+        <v>0.05953695461388201</v>
       </c>
       <c r="O78" t="n">
         <v>-0.05230092059847635</v>
@@ -5011,7 +5011,7 @@
         <v>8.82228163422023</v>
       </c>
       <c r="K79" t="n">
-        <v>18.5792349726776</v>
+        <v>18.42818428184282</v>
       </c>
       <c r="L79" t="n">
         <v>12</v>
@@ -5069,7 +5069,7 @@
         <v>9.379507611538331</v>
       </c>
       <c r="K80" t="n">
-        <v>21.31147540983606</v>
+        <v>21.13821138211382</v>
       </c>
       <c r="L80" t="n">
         <v>14</v>
@@ -5127,7 +5127,7 @@
         <v>12.2526415215383</v>
       </c>
       <c r="K81" t="n">
-        <v>26.22950819672131</v>
+        <v>26.01626016260163</v>
       </c>
       <c r="L81" t="n">
         <v>12</v>
@@ -5170,13 +5170,13 @@
         </is>
       </c>
       <c r="F82" t="n">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="G82" t="n">
-        <v>0.3828144628263419</v>
+        <v>0.3652863920818722</v>
       </c>
       <c r="H82" t="n">
-        <v>0.9599538932805715</v>
+        <v>0.9551808667445858</v>
       </c>
       <c r="I82" t="n">
         <v>-1.84891564322378</v>
@@ -5185,19 +5185,19 @@
         <v>3.20100406514402</v>
       </c>
       <c r="K82" t="n">
-        <v>33.87978142076503</v>
+        <v>34.41734417344173</v>
       </c>
       <c r="L82" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="M82" t="n">
-        <v>9.538461538461538</v>
+        <v>9.071428571428571</v>
       </c>
       <c r="N82" t="n">
-        <v>0.03726867862913498</v>
+        <v>0.03383966205807919</v>
       </c>
       <c r="O82" t="n">
-        <v>-0.008573258647496917</v>
+        <v>-0.01073755336564608</v>
       </c>
       <c r="P82" t="n">
         <v>0.1088088975691219</v>
@@ -5243,7 +5243,7 @@
         <v>2.10200029059912</v>
       </c>
       <c r="K83" t="n">
-        <v>18.5792349726776</v>
+        <v>18.42818428184282</v>
       </c>
       <c r="L83" t="n">
         <v>12</v>
@@ -5301,7 +5301,7 @@
         <v>3.69680550852241</v>
       </c>
       <c r="K84" t="n">
-        <v>21.31147540983606</v>
+        <v>21.13821138211382</v>
       </c>
       <c r="L84" t="n">
         <v>14</v>
@@ -5359,7 +5359,7 @@
         <v>3.04477020602219</v>
       </c>
       <c r="K85" t="n">
-        <v>26.22950819672131</v>
+        <v>26.01626016260163</v>
       </c>
       <c r="L85" t="n">
         <v>12</v>
@@ -5402,13 +5402,13 @@
         </is>
       </c>
       <c r="F86" t="n">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="G86" t="n">
-        <v>0.4890826331747369</v>
+        <v>0.478234057274475</v>
       </c>
       <c r="H86" t="n">
-        <v>1.228835199326766</v>
+        <v>1.212836052847799</v>
       </c>
       <c r="I86" t="n">
         <v>-2.46847418568061</v>
@@ -5417,19 +5417,19 @@
         <v>4.07926854837464</v>
       </c>
       <c r="K86" t="n">
-        <v>34.68013468013468</v>
+        <v>35.33333333333334</v>
       </c>
       <c r="L86" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="M86" t="n">
-        <v>10.3</v>
+        <v>9.636363636363637</v>
       </c>
       <c r="N86" t="n">
-        <v>0.05164701793971523</v>
+        <v>0.04724059318848781</v>
       </c>
       <c r="O86" t="n">
-        <v>0.006721268502088762</v>
+        <v>0.003176345676213721</v>
       </c>
       <c r="P86" t="n">
         <v>0.147091697954961</v>
@@ -5475,7 +5475,7 @@
         <v>2.65425684189646</v>
       </c>
       <c r="K87" t="n">
-        <v>17.17171717171717</v>
+        <v>17</v>
       </c>
       <c r="L87" t="n">
         <v>10</v>
@@ -5533,7 +5533,7 @@
         <v>2.70357383659126</v>
       </c>
       <c r="K88" t="n">
-        <v>19.52861952861953</v>
+        <v>19.33333333333333</v>
       </c>
       <c r="L88" t="n">
         <v>11</v>
@@ -5591,7 +5591,7 @@
         <v>3.89681829021909</v>
       </c>
       <c r="K89" t="n">
-        <v>28.61952861952862</v>
+        <v>28.33333333333333</v>
       </c>
       <c r="L89" t="n">
         <v>11</v>
@@ -5634,13 +5634,13 @@
         </is>
       </c>
       <c r="F90" t="n">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="G90" t="n">
-        <v>0.9439149689520268</v>
+        <v>0.9641448209420704</v>
       </c>
       <c r="H90" t="n">
-        <v>1.769106171540513</v>
+        <v>1.747137949414292</v>
       </c>
       <c r="I90" t="n">
         <v>-6.929464541376349</v>
@@ -5649,16 +5649,16 @@
         <v>6.0219237887344</v>
       </c>
       <c r="K90" t="n">
-        <v>35.94306049822064</v>
+        <v>36.61971830985916</v>
       </c>
       <c r="L90" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="M90" t="n">
-        <v>10.1</v>
+        <v>9.454545454545455</v>
       </c>
       <c r="N90" t="n">
-        <v>0.1020296187396682</v>
+        <v>0.09731537790072316</v>
       </c>
       <c r="O90" t="n">
         <v>-0.03760363205684969</v>
@@ -5707,7 +5707,7 @@
         <v>3.85016947536215</v>
       </c>
       <c r="K91" t="n">
-        <v>18.14946619217082</v>
+        <v>17.95774647887324</v>
       </c>
       <c r="L91" t="n">
         <v>10</v>
@@ -5765,7 +5765,7 @@
         <v>10.5353534010951</v>
       </c>
       <c r="K92" t="n">
-        <v>20.2846975088968</v>
+        <v>20.07042253521127</v>
       </c>
       <c r="L92" t="n">
         <v>10</v>
@@ -5823,7 +5823,7 @@
         <v>6.57176964259876</v>
       </c>
       <c r="K93" t="n">
-        <v>25.62277580071174</v>
+        <v>25.35211267605634</v>
       </c>
       <c r="L93" t="n">
         <v>10</v>
@@ -6122,13 +6122,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{099D5EDE-B862-4198-96B1-2C5A2765043F}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D428E8DC-AC6D-4C15-A6B3-2F0072EC500D}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7C11C7B4-BD83-4E8B-86F6-63A516D64913}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CA83D749-94FE-4706-B2E1-36CAFF7A82A5}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AA2664F9-5AB4-40E5-A790-F9D7EA900E67}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BC38ACA5-0D21-415B-B953-E75B97044D98}"/>
 </file>